--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_32_36.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_32_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2243573.814100159</v>
+        <v>2235306.171435907</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19436261.64045927</v>
+        <v>19436261.64045928</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19436261.64045927</v>
+        <v>19436261.64045928</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37305508.11303175</v>
+        <v>37305508.11303176</v>
       </c>
     </row>
   </sheetData>
@@ -657,10 +657,10 @@
         <v>81.99931295557428</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299369</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984956</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>4.36328960686842</v>
@@ -672,10 +672,10 @@
         <v>2.04078937244312</v>
       </c>
       <c r="H2" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>83.90259686861427</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -687,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>74.55729732774662</v>
       </c>
       <c r="N2" t="n">
-        <v>74.55729732774597</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,16 +708,16 @@
         <v>55.73153463649352</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>179.161240020021</v>
       </c>
       <c r="U2" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>78.24199479138842</v>
+        <v>229.8510241668237</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>207.9969049700139</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -748,49 +748,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>247</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>217.5575999999999</v>
+        <v>247</v>
       </c>
       <c r="T3" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>217.5576000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18.7885671459268</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>18.7885671459268</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -894,25 +894,25 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011742</v>
+        <v>74.50830267924312</v>
       </c>
       <c r="G5" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>247</v>
       </c>
       <c r="I5" t="n">
-        <v>83.90259686861427</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -924,10 +924,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>74.55729732774624</v>
       </c>
       <c r="N5" t="n">
-        <v>74.55729732774597</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>128.7653744233739</v>
+        <v>143.0492973207568</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -979,16 +979,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>217.5575999999999</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>247</v>
+        <v>217.5576000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>18.7885671459268</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>18.7885671459268</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>247</v>
@@ -1161,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>74.55729732774668</v>
       </c>
       <c r="N8" t="n">
-        <v>74.55729732774597</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>217.5575999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="X8" t="n">
-        <v>168.0830217570059</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217.5576000000001</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1222,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>217.5575999999999</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1267,16 +1267,16 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>18.7885671459268</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>18.78856714592684</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>74.55729732774608</v>
+        <v>74.5572973277459</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>179.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>174.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>171.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>22.65510445066185</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>121.9634440104514</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>18.19747798988661</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>236.8896287080119</v>
+        <v>230.5168106275565</v>
       </c>
       <c r="G14" t="n">
         <v>234.0407893724434</v>
       </c>
       <c r="H14" t="n">
-        <v>222.4297039296581</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>74.55729732774601</v>
       </c>
       <c r="N14" t="n">
-        <v>74.55729732774587</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1659,13 +1659,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>216.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>193.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>179.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1732,19 +1732,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="T15" t="n">
-        <v>232.8969975765951</v>
+        <v>121.9634440104514</v>
       </c>
       <c r="U15" t="n">
-        <v>232.1499352318849</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>246.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>106.3828559677419</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>76.27387284153004</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>31.76582899528082</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>214.4225578045526</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>74.55729732774631</v>
+        <v>74.5572973277462</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
         <v>216.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>193.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>179.9376868977026</v>
+        <v>15.8511081217885</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>232.1499352318849</v>
       </c>
       <c r="V18" t="n">
-        <v>136.8135087785666</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>247</v>
@@ -2088,13 +2088,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>8.087106697898495</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>234.0407893724434</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>222.4297039296581</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>74.55729732774597</v>
+        <v>74.55729732774613</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2133,13 +2133,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="V20" t="n">
-        <v>217.5575999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>216.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>193.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>179.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2209,13 +2209,13 @@
         <v>247</v>
       </c>
       <c r="T21" t="n">
-        <v>233.6557557835515</v>
+        <v>121.9634440104513</v>
       </c>
       <c r="U21" t="n">
-        <v>232.1499352318849</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>245.7519089845636</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>42.29215584563042</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2261,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>31.06077380114307</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>141.0696281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>214.4225578045526</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2322,16 +2322,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>18.19747798988661</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>236.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>234.0407893724434</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>222.4297039296581</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2346,11 +2346,11 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>74.55729732774597</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>217.5575999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>216.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>104.1519122922555</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>155.2977664317042</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>17.50421608002777</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2443,25 +2443,25 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="T24" t="n">
-        <v>233.6557557835515</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>232.1499352318849</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>246.51066719152</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>232.896997576595</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>231.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2498,10 +2498,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>31.06077380114307</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>141.0696281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2522,16 +2522,16 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>180.9544797028555</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>16.72443318979342</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>16.74364491190377</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.29215584563042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-1.309603139780384e-12</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2583,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>105.4251488663142</v>
+        <v>95.84518794382484</v>
       </c>
       <c r="N26" t="n">
-        <v>23.95477716531258</v>
+        <v>33.5347380878028</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2607,19 +2607,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>192.014400000002</v>
+        <v>218</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>218</v>
+        <v>192.0144000000013</v>
       </c>
     </row>
     <row r="27">
@@ -2638,16 +2638,16 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>195.6720972219126</v>
+        <v>15.71663356829627</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>177.8210830448387</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>36.52121973325002</v>
+        <v>176.2977664317042</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2692,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28">
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>162.8632671459268</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2774,10 +2774,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>100.4436454301076</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>62.41962171581921</v>
       </c>
     </row>
     <row r="29">
@@ -2790,10 +2790,10 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>192.0144000000024</v>
+        <v>218</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2820,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>129.3799260316269</v>
+        <v>120.4251488663154</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>8.954777165312578</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>218.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>218.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>192.0144</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>218.0000000000002</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30">
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>218.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2878,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>62.39133444343079</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>162.8210830448387</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>161.2977664317042</v>
       </c>
       <c r="I30" t="n">
-        <v>23.50421608002777</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="T30" t="n">
-        <v>218.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>30.71663356829583</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31">
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>196.7807578045525</v>
       </c>
       <c r="N31" t="n">
-        <v>196.7807578045525</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="G32" t="n">
-        <v>192.0144000000012</v>
+        <v>192.0144</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>129.3799260316266</v>
+        <v>129.3799260316277</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="W32" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>161.2977664317042</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,22 +3151,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="T33" t="n">
-        <v>218.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="V33" t="n">
-        <v>30.71663356829706</v>
+        <v>192.0144000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>218.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3194,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>112.3828559677419</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>82.27387284153004</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.124028995280542</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>37.06077380114307</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>147.0696281577792</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>12.65035584563022</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="D35" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3294,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>120.4251488663138</v>
+        <v>120.4251488663154</v>
       </c>
       <c r="N35" t="n">
         <v>8.954777165312578</v>
@@ -3318,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>192.0144</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>192.0144000000014</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>199.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>30.71663356829729</v>
+        <v>162.8210830448387</v>
       </c>
       <c r="H36" t="n">
         <v>161.2977664317042</v>
@@ -3394,22 +3394,22 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>104.7956380779379</v>
       </c>
     </row>
     <row r="37">
@@ -3464,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>196.7807578045525</v>
       </c>
       <c r="R37" t="n">
-        <v>196.7807578045525</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3510,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>218.0000000000004</v>
+        <v>192.0144</v>
       </c>
       <c r="G38" t="n">
-        <v>192.0144000000014</v>
+        <v>218</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3531,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>80.84518794382484</v>
       </c>
       <c r="N38" t="n">
-        <v>129.3799260316266</v>
+        <v>48.53473808780334</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="W38" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>161.2977664317042</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,19 +3628,19 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>30.71663356829718</v>
+        <v>192.0144000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="V39" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>112.3828559677419</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2.602561529409701</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         <v>37.06077380114307</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>147.0696281577792</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3707,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>12.65035584563022</v>
       </c>
       <c r="T40" t="n">
-        <v>44.73456650625771</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3738,16 +3738,16 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="D41" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>129.3799260316269</v>
+        <v>129.3799260316281</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3786,16 +3786,16 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="T41" t="n">
-        <v>192.0144000000014</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>192.0144000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>192.0144000000015</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H42" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3868,19 +3868,19 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>192.0144</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>33.49006714592675</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>33.49006714592679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3978,19 +3978,19 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="G44" t="n">
-        <v>192.0144000000015</v>
+        <v>218</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>129.3799260316259</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>129.3799260316274</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>218.0000000000004</v>
+        <v>192.0144</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="G45" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="H45" t="n">
-        <v>218.0000000000004</v>
+        <v>192.0143999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>185.5042160800278</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.510183919973955</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
         <v>18.7885671459268</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4297,28 +4297,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>375.856424541199</v>
+        <v>81.14210700032007</v>
       </c>
       <c r="C2" t="n">
-        <v>375.856424541199</v>
+        <v>31.16778554275068</v>
       </c>
       <c r="D2" t="n">
-        <v>365.4128328847853</v>
+        <v>31.16778554275068</v>
       </c>
       <c r="E2" t="n">
-        <v>361.0054696455243</v>
+        <v>26.76042230348965</v>
       </c>
       <c r="F2" t="n">
-        <v>356.0664507485428</v>
+        <v>21.8214034065082</v>
       </c>
       <c r="G2" t="n">
-        <v>354.0050473420346</v>
+        <v>19.76</v>
       </c>
       <c r="H2" t="n">
-        <v>104.5100978470851</v>
+        <v>19.76</v>
       </c>
       <c r="I2" t="n">
-        <v>19.76000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="J2" t="n">
         <v>129.3033246716319</v>
@@ -4327,10 +4327,10 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L2" t="n">
-        <v>590.0055507520343</v>
+        <v>590.005550752035</v>
       </c>
       <c r="M2" t="n">
-        <v>590.0055507520343</v>
+        <v>514.6951494108768</v>
       </c>
       <c r="N2" t="n">
         <v>514.6951494108768</v>
@@ -4351,22 +4351,22 @@
         <v>787.2112808512624</v>
       </c>
       <c r="T2" t="n">
-        <v>787.2112808512624</v>
+        <v>606.2403313360896</v>
       </c>
       <c r="U2" t="n">
-        <v>537.7163313563128</v>
+        <v>606.2403313360896</v>
       </c>
       <c r="V2" t="n">
-        <v>458.6840133852134</v>
+        <v>374.0675796524293</v>
       </c>
       <c r="W2" t="n">
-        <v>458.6840133852134</v>
+        <v>163.9696958443345</v>
       </c>
       <c r="X2" t="n">
-        <v>458.6840133852134</v>
+        <v>163.9696958443345</v>
       </c>
       <c r="Y2" t="n">
-        <v>458.6840133852134</v>
+        <v>163.9696958443345</v>
       </c>
     </row>
     <row r="3">
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>269.2549494949495</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="C3" t="n">
-        <v>269.2549494949495</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="D3" t="n">
-        <v>269.2549494949495</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="E3" t="n">
-        <v>269.2549494949495</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="F3" t="n">
-        <v>269.2549494949495</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="G3" t="n">
         <v>19.75999999999999</v>
@@ -4397,22 +4397,22 @@
         <v>19.75999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>19.76000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="J3" t="n">
-        <v>19.76000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="K3" t="n">
-        <v>100.6406022243355</v>
+        <v>264.29</v>
       </c>
       <c r="L3" t="n">
-        <v>185.2094947809393</v>
+        <v>353.2139643818132</v>
       </c>
       <c r="M3" t="n">
-        <v>429.7394947809393</v>
+        <v>597.7439643818132</v>
       </c>
       <c r="N3" t="n">
-        <v>674.2694947809392</v>
+        <v>842.2739643818131</v>
       </c>
       <c r="O3" t="n">
         <v>918.7994947809392</v>
@@ -4424,28 +4424,28 @@
         <v>988</v>
       </c>
       <c r="R3" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="S3" t="n">
-        <v>768.2448484848486</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="T3" t="n">
-        <v>518.7498989898991</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="U3" t="n">
-        <v>518.7498989898991</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="V3" t="n">
-        <v>518.7498989898991</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="W3" t="n">
-        <v>518.7498989898991</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="X3" t="n">
-        <v>269.2549494949495</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="Y3" t="n">
-        <v>269.2549494949495</v>
+        <v>269.2549494949493</v>
       </c>
     </row>
     <row r="4">
@@ -4491,16 +4491,16 @@
         <v>38.73835065245108</v>
       </c>
       <c r="N4" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="O4" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="P4" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="Q4" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="R4" t="n">
         <v>19.75999999999976</v>
@@ -4534,28 +4534,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>608.4390157339657</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="C5" t="n">
-        <v>608.4390157339657</v>
+        <v>594.0108107871143</v>
       </c>
       <c r="D5" t="n">
-        <v>608.4390157339657</v>
+        <v>594.0108107871143</v>
       </c>
       <c r="E5" t="n">
-        <v>608.4390157339657</v>
+        <v>344.5158612921648</v>
       </c>
       <c r="F5" t="n">
-        <v>603.4999968369841</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="G5" t="n">
-        <v>354.0050473420346</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="H5" t="n">
-        <v>104.5100978470851</v>
+        <v>19.76</v>
       </c>
       <c r="I5" t="n">
-        <v>19.76000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="J5" t="n">
         <v>129.3033246716319</v>
@@ -4564,10 +4564,10 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L5" t="n">
-        <v>590.0055507520343</v>
+        <v>590.0055507520345</v>
       </c>
       <c r="M5" t="n">
-        <v>590.0055507520343</v>
+        <v>514.6951494108768</v>
       </c>
       <c r="N5" t="n">
         <v>514.6951494108768</v>
@@ -4582,28 +4582,28 @@
         <v>988</v>
       </c>
       <c r="R5" t="n">
-        <v>857.9339652289152</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="S5" t="n">
-        <v>857.9339652289152</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="T5" t="n">
-        <v>857.9339652289152</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="U5" t="n">
-        <v>608.4390157339657</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="V5" t="n">
-        <v>608.4390157339657</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="W5" t="n">
-        <v>608.4390157339657</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="X5" t="n">
-        <v>608.4390157339657</v>
+        <v>843.5057602820639</v>
       </c>
       <c r="Y5" t="n">
-        <v>608.4390157339657</v>
+        <v>843.5057602820639</v>
       </c>
     </row>
     <row r="6">
@@ -4613,40 +4613,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>489.0101010101009</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="C6" t="n">
-        <v>489.0101010101009</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="D6" t="n">
-        <v>489.0101010101009</v>
+        <v>269.2549494949493</v>
       </c>
       <c r="E6" t="n">
-        <v>489.0101010101009</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="F6" t="n">
-        <v>489.0101010101009</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="G6" t="n">
-        <v>239.5151515151514</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>19.76000000000001</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>19.76000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="J6" t="n">
-        <v>50.21730874389269</v>
+        <v>19.76</v>
       </c>
       <c r="K6" t="n">
-        <v>93.31557704427009</v>
+        <v>264.29</v>
       </c>
       <c r="L6" t="n">
-        <v>177.8844696008739</v>
+        <v>348.8588925566038</v>
       </c>
       <c r="M6" t="n">
-        <v>422.4144696008739</v>
+        <v>593.3888925566038</v>
       </c>
       <c r="N6" t="n">
         <v>666.9444696008738</v>
@@ -4673,16 +4673,16 @@
         <v>988</v>
       </c>
       <c r="V6" t="n">
-        <v>738.5050505050505</v>
+        <v>768.2448484848484</v>
       </c>
       <c r="W6" t="n">
-        <v>738.5050505050505</v>
+        <v>768.2448484848484</v>
       </c>
       <c r="X6" t="n">
-        <v>489.0101010101009</v>
+        <v>518.7498989898988</v>
       </c>
       <c r="Y6" t="n">
-        <v>489.0101010101009</v>
+        <v>518.7498989898988</v>
       </c>
     </row>
     <row r="7">
@@ -4728,16 +4728,16 @@
         <v>38.73835065245108</v>
       </c>
       <c r="N7" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="O7" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="P7" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.73835065245108</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="R7" t="n">
         <v>19.75999999999976</v>
@@ -4771,28 +4771,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>818.2191699424183</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="C8" t="n">
-        <v>768.2448484848486</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="D8" t="n">
-        <v>768.2448484848486</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="E8" t="n">
-        <v>518.7498989898991</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="F8" t="n">
         <v>269.2549494949495</v>
       </c>
       <c r="G8" t="n">
-        <v>19.76000000000001</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>19.76000000000001</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>19.76000000000001</v>
+        <v>19.76</v>
       </c>
       <c r="J8" t="n">
         <v>129.3033246716319</v>
@@ -4801,10 +4801,10 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L8" t="n">
-        <v>590.0055507520343</v>
+        <v>590.005550752035</v>
       </c>
       <c r="M8" t="n">
-        <v>590.0055507520343</v>
+        <v>514.6951494108768</v>
       </c>
       <c r="N8" t="n">
         <v>514.6951494108768</v>
@@ -4828,19 +4828,19 @@
         <v>988</v>
       </c>
       <c r="U8" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="V8" t="n">
-        <v>988</v>
+        <v>518.7498989898991</v>
       </c>
       <c r="W8" t="n">
-        <v>988</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="X8" t="n">
-        <v>818.2191699424183</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="Y8" t="n">
-        <v>818.2191699424183</v>
+        <v>269.2549494949495</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.75999999999976</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="C9" t="n">
-        <v>19.76000000000001</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="D9" t="n">
-        <v>19.76000000000001</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="E9" t="n">
-        <v>19.76000000000001</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="F9" t="n">
-        <v>19.76000000000001</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="G9" t="n">
-        <v>19.76000000000001</v>
+        <v>239.5151515151514</v>
       </c>
       <c r="H9" t="n">
         <v>19.76000000000001</v>
@@ -4874,22 +4874,22 @@
         <v>19.76000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>19.76000000000001</v>
+        <v>225.546803524832</v>
       </c>
       <c r="K9" t="n">
-        <v>62.8582683003774</v>
+        <v>268.6450718252094</v>
       </c>
       <c r="L9" t="n">
-        <v>147.4271608569812</v>
+        <v>353.2139643818132</v>
       </c>
       <c r="M9" t="n">
-        <v>254.4100000000001</v>
+        <v>597.7439643818132</v>
       </c>
       <c r="N9" t="n">
-        <v>498.9400000000001</v>
+        <v>842.2739643818131</v>
       </c>
       <c r="O9" t="n">
-        <v>743.47</v>
+        <v>918.7994947809392</v>
       </c>
       <c r="P9" t="n">
         <v>988</v>
@@ -4910,16 +4910,16 @@
         <v>738.5050505050505</v>
       </c>
       <c r="V9" t="n">
-        <v>738.5050505050505</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="W9" t="n">
-        <v>738.5050505050505</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="X9" t="n">
         <v>489.0101010101009</v>
       </c>
       <c r="Y9" t="n">
-        <v>239.5151515151514</v>
+        <v>489.0101010101009</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="C10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="D10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="E10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="F10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="G10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="H10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="I10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="J10" t="n">
-        <v>38.73835065245108</v>
+        <v>988</v>
       </c>
       <c r="K10" t="n">
-        <v>38.73835065245108</v>
+        <v>988</v>
       </c>
       <c r="L10" t="n">
-        <v>38.73835065245108</v>
+        <v>988</v>
       </c>
       <c r="M10" t="n">
-        <v>38.73835065245108</v>
+        <v>988</v>
       </c>
       <c r="N10" t="n">
-        <v>19.75999999999976</v>
+        <v>988</v>
       </c>
       <c r="O10" t="n">
-        <v>19.75999999999976</v>
+        <v>988</v>
       </c>
       <c r="P10" t="n">
-        <v>19.75999999999976</v>
+        <v>988</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="R10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="S10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="T10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="U10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="V10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="W10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="X10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.75999999999976</v>
+        <v>969.0216493475486</v>
       </c>
     </row>
     <row r="11">
@@ -5026,7 +5026,7 @@
         <v>244.4364686158162</v>
       </c>
       <c r="H11" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>19.75999999999999</v>
@@ -5038,7 +5038,7 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L11" t="n">
-        <v>590.0055507520344</v>
+        <v>590.0055507520342</v>
       </c>
       <c r="M11" t="n">
         <v>514.6951494108768</v>
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>769.2560033875488</v>
+        <v>396.5656559022444</v>
       </c>
       <c r="C12" t="n">
-        <v>574.2055867759132</v>
+        <v>201.5152392906087</v>
       </c>
       <c r="D12" t="n">
-        <v>392.4503474853044</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>216.0138856449886</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>42.64394388955742</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>19.75999999999999</v>
@@ -5111,19 +5111,19 @@
         <v>19.75999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>97.80787844455382</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>307.2261467449312</v>
+        <v>229.1782683003774</v>
       </c>
       <c r="L12" t="n">
-        <v>398.5951356893123</v>
+        <v>313.7471608569812</v>
       </c>
       <c r="M12" t="n">
-        <v>398.5951356893123</v>
+        <v>471.5395973455089</v>
       </c>
       <c r="N12" t="n">
-        <v>398.5951356893123</v>
+        <v>471.5395973455089</v>
       </c>
       <c r="O12" t="n">
         <v>641.4406660884384</v>
@@ -5138,25 +5138,25 @@
         <v>988</v>
       </c>
       <c r="S12" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="T12" t="n">
-        <v>988</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="U12" t="n">
-        <v>988</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="V12" t="n">
-        <v>988</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="W12" t="n">
-        <v>988</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="X12" t="n">
-        <v>988</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="Y12" t="n">
-        <v>988</v>
+        <v>615.3096525146955</v>
       </c>
     </row>
     <row r="13">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>738.5050505050505</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="C14" t="n">
-        <v>738.5050505050505</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="D14" t="n">
-        <v>738.5050505050505</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="E14" t="n">
-        <v>720.1237596061751</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="F14" t="n">
-        <v>480.841306365759</v>
+        <v>256.1648377499428</v>
       </c>
       <c r="G14" t="n">
-        <v>244.4364686158162</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>19.75999999999999</v>
@@ -5275,10 +5275,10 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L14" t="n">
-        <v>590.0055507520342</v>
+        <v>590.0055507520343</v>
       </c>
       <c r="M14" t="n">
-        <v>590.0055507520342</v>
+        <v>514.6951494108768</v>
       </c>
       <c r="N14" t="n">
         <v>514.6951494108768</v>
@@ -5302,10 +5302,10 @@
         <v>988</v>
       </c>
       <c r="U14" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="V14" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="W14" t="n">
         <v>738.5050505050505</v>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.75999999999999</v>
+        <v>396.5656559022444</v>
       </c>
       <c r="C15" t="n">
-        <v>19.75999999999999</v>
+        <v>201.5152392906087</v>
       </c>
       <c r="D15" t="n">
         <v>19.75999999999999</v>
@@ -5348,25 +5348,25 @@
         <v>19.75999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>42.52670713705385</v>
+        <v>170.7523401007507</v>
       </c>
       <c r="K15" t="n">
-        <v>251.9449754374313</v>
+        <v>380.1706084011281</v>
       </c>
       <c r="L15" t="n">
-        <v>336.513867994035</v>
+        <v>464.7395009577319</v>
       </c>
       <c r="M15" t="n">
-        <v>336.513867994035</v>
+        <v>480.5500204747847</v>
       </c>
       <c r="N15" t="n">
-        <v>500.6244696008739</v>
+        <v>480.5500204747847</v>
       </c>
       <c r="O15" t="n">
-        <v>743.47</v>
+        <v>723.3955508739109</v>
       </c>
       <c r="P15" t="n">
-        <v>988</v>
+        <v>958.9160560929718</v>
       </c>
       <c r="Q15" t="n">
         <v>988</v>
@@ -5375,25 +5375,25 @@
         <v>988</v>
       </c>
       <c r="S15" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="T15" t="n">
-        <v>752.7505074983887</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="U15" t="n">
-        <v>518.2556234257778</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="V15" t="n">
-        <v>269.2549494949493</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="W15" t="n">
-        <v>19.75999999999976</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="X15" t="n">
-        <v>19.75999999999999</v>
+        <v>615.3096525146955</v>
       </c>
       <c r="Y15" t="n">
-        <v>19.75999999999999</v>
+        <v>615.3096525146955</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="C16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="D16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="E16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="F16" t="n">
-        <v>880.5425697295536</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="G16" t="n">
-        <v>803.4982537280082</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="H16" t="n">
-        <v>771.4115577731791</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="I16" t="n">
-        <v>785.788876709262</v>
+        <v>51.05009157436932</v>
       </c>
       <c r="J16" t="n">
-        <v>971.0872273617133</v>
+        <v>236.3484422268206</v>
       </c>
       <c r="K16" t="n">
-        <v>971.0872273617133</v>
+        <v>236.3484422268206</v>
       </c>
       <c r="L16" t="n">
-        <v>971.0872273617133</v>
+        <v>236.3484422268206</v>
       </c>
       <c r="M16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="N16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="O16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="P16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="Q16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="R16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="S16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="T16" t="n">
-        <v>971.0872273617133</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="U16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="V16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="W16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="X16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
       <c r="Y16" t="n">
-        <v>988</v>
+        <v>36.6727726382864</v>
       </c>
     </row>
     <row r="17">
@@ -5512,7 +5512,7 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L17" t="n">
-        <v>590.0055507520347</v>
+        <v>590.0055507520345</v>
       </c>
       <c r="M17" t="n">
         <v>514.6951494108768</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>396.5656559022444</v>
+        <v>35.77122032503888</v>
       </c>
       <c r="C18" t="n">
-        <v>201.5152392906087</v>
+        <v>35.77122032503888</v>
       </c>
       <c r="D18" t="n">
         <v>19.75999999999999</v>
@@ -5585,52 +5585,52 @@
         <v>19.75999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>170.7523401007507</v>
+        <v>264.29</v>
       </c>
       <c r="K18" t="n">
-        <v>380.1706084011281</v>
+        <v>307.3882683003774</v>
       </c>
       <c r="L18" t="n">
-        <v>464.7395009577319</v>
+        <v>391.9571608569811</v>
       </c>
       <c r="M18" t="n">
-        <v>654.9620407356074</v>
+        <v>462.5301025645702</v>
       </c>
       <c r="N18" t="n">
-        <v>654.9620407356074</v>
+        <v>462.5301025645701</v>
       </c>
       <c r="O18" t="n">
-        <v>897.8075711347335</v>
+        <v>632.4311713074993</v>
       </c>
       <c r="P18" t="n">
-        <v>967.0080763537943</v>
+        <v>876.9611713074993</v>
       </c>
       <c r="Q18" t="n">
         <v>988</v>
       </c>
       <c r="R18" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="S18" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="T18" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="U18" t="n">
-        <v>753.5051159273891</v>
+        <v>504.0101664324395</v>
       </c>
       <c r="V18" t="n">
-        <v>615.3096525146955</v>
+        <v>504.0101664324395</v>
       </c>
       <c r="W18" t="n">
-        <v>615.3096525146955</v>
+        <v>254.51521693749</v>
       </c>
       <c r="X18" t="n">
-        <v>615.3096525146955</v>
+        <v>254.51521693749</v>
       </c>
       <c r="Y18" t="n">
-        <v>615.3096525146955</v>
+        <v>254.51521693749</v>
       </c>
     </row>
     <row r="19">
@@ -5719,28 +5719,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>269.2549494949495</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="C20" t="n">
-        <v>19.75999999999999</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="D20" t="n">
-        <v>19.75999999999999</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="E20" t="n">
-        <v>19.75999999999976</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="F20" t="n">
-        <v>19.75999999999976</v>
+        <v>480.841306365759</v>
       </c>
       <c r="G20" t="n">
-        <v>19.76000000000001</v>
+        <v>244.4364686158162</v>
       </c>
       <c r="H20" t="n">
         <v>19.76000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>19.76000000000001</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>129.3033246716319</v>
@@ -5749,7 +5749,7 @@
         <v>345.4755507520339</v>
       </c>
       <c r="L20" t="n">
-        <v>590.0055507520343</v>
+        <v>590.0055507520344</v>
       </c>
       <c r="M20" t="n">
         <v>514.6951494108768</v>
@@ -5776,19 +5776,19 @@
         <v>988</v>
       </c>
       <c r="U20" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="V20" t="n">
-        <v>768.2448484848486</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="W20" t="n">
-        <v>518.7498989898991</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="X20" t="n">
-        <v>518.7498989898991</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="Y20" t="n">
-        <v>518.7498989898991</v>
+        <v>738.5050505050505</v>
       </c>
     </row>
     <row r="21">
@@ -5798,46 +5798,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.75999999999999</v>
+        <v>396.5656559022444</v>
       </c>
       <c r="C21" t="n">
-        <v>19.75999999999999</v>
+        <v>201.5152392906087</v>
       </c>
       <c r="D21" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>170.7523401007507</v>
       </c>
       <c r="K21" t="n">
-        <v>380.1706084011281</v>
+        <v>315.3181670057538</v>
       </c>
       <c r="L21" t="n">
-        <v>464.7395009577319</v>
+        <v>399.8870595623575</v>
       </c>
       <c r="M21" t="n">
-        <v>599.4306671786187</v>
+        <v>415.6975790794104</v>
       </c>
       <c r="N21" t="n">
-        <v>654.9620407356068</v>
+        <v>415.6975790794104</v>
       </c>
       <c r="O21" t="n">
-        <v>731.4875711347329</v>
+        <v>658.5431094785365</v>
       </c>
       <c r="P21" t="n">
         <v>894.0636146975974</v>
@@ -5852,22 +5852,22 @@
         <v>738.5050505050505</v>
       </c>
       <c r="T21" t="n">
-        <v>502.4891355721701</v>
+        <v>615.3096525146956</v>
       </c>
       <c r="U21" t="n">
-        <v>267.9942514995591</v>
+        <v>615.3096525146956</v>
       </c>
       <c r="V21" t="n">
-        <v>19.75999999999999</v>
+        <v>615.3096525146956</v>
       </c>
       <c r="W21" t="n">
-        <v>19.75999999999999</v>
+        <v>615.3096525146956</v>
       </c>
       <c r="X21" t="n">
-        <v>19.75999999999999</v>
+        <v>615.3096525146956</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.75999999999999</v>
+        <v>615.3096525146956</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="C22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="D22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="E22" t="n">
-        <v>36.67277263828663</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="F22" t="n">
-        <v>36.67277263828663</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="G22" t="n">
-        <v>36.67277263828663</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="H22" t="n">
-        <v>36.67277263828663</v>
+        <v>19.75999999999976</v>
       </c>
       <c r="I22" t="n">
-        <v>51.05009157436955</v>
+        <v>34.13731893608268</v>
       </c>
       <c r="J22" t="n">
-        <v>236.3484422268209</v>
+        <v>219.435669588534</v>
       </c>
       <c r="K22" t="n">
-        <v>236.3484422268209</v>
+        <v>188.0611505974804</v>
       </c>
       <c r="L22" t="n">
-        <v>236.3484422268209</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="M22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="N22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="O22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="P22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="Q22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="R22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="S22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="T22" t="n">
-        <v>19.75999999999999</v>
+        <v>45.56657670073375</v>
       </c>
       <c r="U22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="V22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="W22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="X22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
       <c r="Y22" t="n">
-        <v>36.67277263828663</v>
+        <v>62.47934933902039</v>
       </c>
     </row>
     <row r="23">
@@ -5956,28 +5956,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>988</v>
+        <v>269.2549494949495</v>
       </c>
       <c r="C23" t="n">
-        <v>738.5050505050505</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>738.5050505050505</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>720.1237596061751</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>480.841306365759</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>244.4364686158162</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>129.3033246716319</v>
@@ -5989,7 +5989,7 @@
         <v>590.0055507520343</v>
       </c>
       <c r="M23" t="n">
-        <v>514.6951494108768</v>
+        <v>590.0055507520343</v>
       </c>
       <c r="N23" t="n">
         <v>514.6951494108768</v>
@@ -6010,22 +6010,22 @@
         <v>988</v>
       </c>
       <c r="T23" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="U23" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="V23" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="W23" t="n">
-        <v>988</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="X23" t="n">
-        <v>988</v>
+        <v>489.0101010101009</v>
       </c>
       <c r="Y23" t="n">
-        <v>988</v>
+        <v>269.2549494949495</v>
       </c>
     </row>
     <row r="24">
@@ -6035,49 +6035,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>299.5114088929166</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>299.5114088929166</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>299.5114088929166</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>299.5114088929166</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>299.5114088929166</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>194.3074570825575</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>37.44102634346239</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>19.75999999999999</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>264.29</v>
+        <v>170.7523401007507</v>
       </c>
       <c r="K24" t="n">
-        <v>473.7082683003774</v>
+        <v>213.8506084011281</v>
       </c>
       <c r="L24" t="n">
-        <v>558.2771608569811</v>
+        <v>458.3806084011281</v>
       </c>
       <c r="M24" t="n">
-        <v>582.0175790794103</v>
+        <v>474.191127918181</v>
       </c>
       <c r="N24" t="n">
-        <v>582.0175790794103</v>
+        <v>563.2306660884385</v>
       </c>
       <c r="O24" t="n">
-        <v>658.5431094785365</v>
+        <v>807.7606660884385</v>
       </c>
       <c r="P24" t="n">
-        <v>894.0636146975974</v>
+        <v>876.9611713074993</v>
       </c>
       <c r="Q24" t="n">
         <v>988</v>
@@ -6086,25 +6086,25 @@
         <v>988</v>
       </c>
       <c r="S24" t="n">
-        <v>988</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="T24" t="n">
-        <v>751.9840850671196</v>
+        <v>738.5050505050505</v>
       </c>
       <c r="U24" t="n">
-        <v>751.9840850671196</v>
+        <v>504.0101664324395</v>
       </c>
       <c r="V24" t="n">
-        <v>751.9840850671196</v>
+        <v>255.0094925016112</v>
       </c>
       <c r="W24" t="n">
-        <v>751.9840850671196</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>751.9840850671196</v>
+        <v>19.76000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>518.2554055053678</v>
+        <v>19.76000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -6141,46 +6141,46 @@
         <v>219.4356695885342</v>
       </c>
       <c r="K25" t="n">
-        <v>188.0611505974806</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="L25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="M25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="N25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="O25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="P25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="Q25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="R25" t="n">
-        <v>45.56657670073398</v>
+        <v>219.4356695885342</v>
       </c>
       <c r="S25" t="n">
-        <v>45.56657670073398</v>
+        <v>36.65336685837718</v>
       </c>
       <c r="T25" t="n">
-        <v>45.56657670073398</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>62.47934933902062</v>
+        <v>36.67277263828663</v>
       </c>
       <c r="V25" t="n">
-        <v>62.47934933902062</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>62.47934933902062</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>62.47934933902062</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="Y25" t="n">
         <v>19.75999999999999</v>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>237.6420202020194</v>
+        <v>17.43999999999892</v>
       </c>
       <c r="C26" t="n">
-        <v>17.43999999999915</v>
+        <v>17.43999999999824</v>
       </c>
       <c r="D26" t="n">
         <v>17.43999999999988</v>
@@ -6214,10 +6214,10 @@
         <v>17.43999999999988</v>
       </c>
       <c r="I26" t="n">
-        <v>17.4399999999996</v>
+        <v>17.43999999999966</v>
       </c>
       <c r="J26" t="n">
-        <v>126.9833246716315</v>
+        <v>126.9833246716316</v>
       </c>
       <c r="K26" t="n">
         <v>342.8033246716319</v>
@@ -6226,43 +6226,43 @@
         <v>558.6233246716323</v>
       </c>
       <c r="M26" t="n">
-        <v>452.133275311719</v>
+        <v>461.8100035162537</v>
       </c>
       <c r="N26" t="n">
-        <v>427.9365307002922</v>
+        <v>427.9365307002913</v>
       </c>
       <c r="O26" t="n">
-        <v>643.7565307002922</v>
+        <v>643.7565307002913</v>
       </c>
       <c r="P26" t="n">
-        <v>859.5765307002921</v>
+        <v>859.5765307002912</v>
       </c>
       <c r="Q26" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="R26" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="S26" t="n">
-        <v>651.7979797979809</v>
+        <v>651.79797979798</v>
       </c>
       <c r="T26" t="n">
-        <v>651.7979797979809</v>
+        <v>651.79797979798</v>
       </c>
       <c r="U26" t="n">
-        <v>651.7979797979809</v>
+        <v>431.5959595959598</v>
       </c>
       <c r="V26" t="n">
-        <v>651.7979797979809</v>
+        <v>431.5959595959598</v>
       </c>
       <c r="W26" t="n">
-        <v>457.8440404040396</v>
+        <v>211.3939393939396</v>
       </c>
       <c r="X26" t="n">
-        <v>457.8440404040396</v>
+        <v>211.3939393939396</v>
       </c>
       <c r="Y26" t="n">
-        <v>237.6420202020194</v>
+        <v>17.43999999999892</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>431.5959595959607</v>
+        <v>211.3939393939396</v>
       </c>
       <c r="C27" t="n">
-        <v>431.5959595959607</v>
+        <v>211.3939393939396</v>
       </c>
       <c r="D27" t="n">
-        <v>431.5959595959607</v>
+        <v>211.3939393939396</v>
       </c>
       <c r="E27" t="n">
-        <v>233.9473765435237</v>
+        <v>195.5185519512161</v>
       </c>
       <c r="F27" t="n">
-        <v>233.9473765435237</v>
+        <v>195.5185519512161</v>
       </c>
       <c r="G27" t="n">
-        <v>54.33012094267656</v>
+        <v>195.5185519512161</v>
       </c>
       <c r="H27" t="n">
         <v>17.43999999999977</v>
@@ -6296,52 +6296,52 @@
         <v>17.43999999999977</v>
       </c>
       <c r="J27" t="n">
-        <v>17.43999999999977</v>
+        <v>147.6423401007505</v>
       </c>
       <c r="K27" t="n">
-        <v>206.0682683003772</v>
+        <v>190.7406084011279</v>
       </c>
       <c r="L27" t="n">
-        <v>421.8882683003771</v>
+        <v>333.5617359215485</v>
       </c>
       <c r="M27" t="n">
-        <v>461.9892925314516</v>
+        <v>333.5617359215485</v>
       </c>
       <c r="N27" t="n">
-        <v>496.7306660884397</v>
+        <v>368.3031094785367</v>
       </c>
       <c r="O27" t="n">
-        <v>712.5506660884397</v>
+        <v>584.1231094785367</v>
       </c>
       <c r="P27" t="n">
-        <v>781.7511713075005</v>
+        <v>798.8536146975975</v>
       </c>
       <c r="Q27" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="R27" t="n">
-        <v>651.7979797979809</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="S27" t="n">
-        <v>651.7979797979809</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>651.7979797979809</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="U27" t="n">
-        <v>431.5959595959607</v>
+        <v>651.79797979798</v>
       </c>
       <c r="V27" t="n">
-        <v>431.5959595959607</v>
+        <v>651.79797979798</v>
       </c>
       <c r="W27" t="n">
-        <v>431.5959595959607</v>
+        <v>431.5959595959598</v>
       </c>
       <c r="X27" t="n">
-        <v>431.5959595959607</v>
+        <v>431.5959595959598</v>
       </c>
       <c r="Y27" t="n">
-        <v>431.5959595959607</v>
+        <v>211.3939393939396</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="C28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="D28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="E28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="F28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="G28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="H28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="I28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
       <c r="J28" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="K28" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="L28" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="M28" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="N28" t="n">
-        <v>872.0000000000011</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="O28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="P28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="Q28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="R28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="S28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="T28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="U28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="V28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="W28" t="n">
-        <v>707.4916493475498</v>
+        <v>872.0000000000002</v>
       </c>
       <c r="X28" t="n">
-        <v>707.4916493475498</v>
+        <v>770.5417722928208</v>
       </c>
       <c r="Y28" t="n">
-        <v>707.4916493475498</v>
+        <v>707.4916493475489</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>211.3939393939405</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="C29" t="n">
-        <v>17.43999999999869</v>
+        <v>237.6420202020202</v>
       </c>
       <c r="D29" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="E29" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="F29" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="G29" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="H29" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="I29" t="n">
-        <v>17.43999999999971</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="J29" t="n">
-        <v>126.9833246716316</v>
+        <v>126.9833246716319</v>
       </c>
       <c r="K29" t="n">
         <v>342.8033246716321</v>
       </c>
       <c r="L29" t="n">
-        <v>558.6233246716325</v>
+        <v>558.6233246716324</v>
       </c>
       <c r="M29" t="n">
-        <v>427.9365307002922</v>
+        <v>436.9817601602027</v>
       </c>
       <c r="N29" t="n">
-        <v>427.9365307002922</v>
+        <v>427.936530700291</v>
       </c>
       <c r="O29" t="n">
-        <v>643.7565307002924</v>
+        <v>643.756530700291</v>
       </c>
       <c r="P29" t="n">
-        <v>859.5765307002926</v>
+        <v>859.576530700291</v>
       </c>
       <c r="Q29" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="R29" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="S29" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="T29" t="n">
-        <v>651.7979797979813</v>
+        <v>872</v>
       </c>
       <c r="U29" t="n">
-        <v>431.5959595959609</v>
+        <v>872</v>
       </c>
       <c r="V29" t="n">
-        <v>431.5959595959609</v>
+        <v>872</v>
       </c>
       <c r="W29" t="n">
-        <v>431.5959595959609</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="X29" t="n">
-        <v>431.5959595959609</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="Y29" t="n">
-        <v>211.3939393939405</v>
+        <v>457.8440404040404</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>431.5959595959609</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="C30" t="n">
-        <v>431.5959595959609</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="D30" t="n">
-        <v>431.5959595959609</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="E30" t="n">
-        <v>431.5959595959609</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="F30" t="n">
-        <v>368.5744096531015</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="G30" t="n">
-        <v>204.1086692037695</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="H30" t="n">
-        <v>41.18163240406835</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="I30" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44</v>
       </c>
       <c r="J30" t="n">
-        <v>162.4923401007506</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="K30" t="n">
-        <v>205.590608401128</v>
+        <v>220.9182683003774</v>
       </c>
       <c r="L30" t="n">
-        <v>378.4741867682668</v>
+        <v>436.7382683003774</v>
       </c>
       <c r="M30" t="n">
-        <v>588.6862055224237</v>
+        <v>446.6087878174303</v>
       </c>
       <c r="N30" t="n">
-        <v>638.2775790794119</v>
+        <v>496.2001613744184</v>
       </c>
       <c r="O30" t="n">
-        <v>714.8031094785381</v>
+        <v>656.1800000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>784.0036146975989</v>
+        <v>872</v>
       </c>
       <c r="Q30" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="R30" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="S30" t="n">
-        <v>872.0000000000016</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="T30" t="n">
-        <v>651.7979797979813</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="U30" t="n">
-        <v>651.7979797979813</v>
+        <v>620.7710772037416</v>
       </c>
       <c r="V30" t="n">
-        <v>651.7979797979813</v>
+        <v>620.7710772037416</v>
       </c>
       <c r="W30" t="n">
-        <v>651.7979797979813</v>
+        <v>400.5690570017214</v>
       </c>
       <c r="X30" t="n">
-        <v>651.7979797979813</v>
+        <v>400.5690570017214</v>
       </c>
       <c r="Y30" t="n">
-        <v>651.7979797979813</v>
+        <v>180.3670367997012</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="C31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="D31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="E31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="F31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="G31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="H31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="I31" t="n">
-        <v>692.6416493475504</v>
+        <v>692.6416493475488</v>
       </c>
       <c r="J31" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="K31" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="L31" t="n">
-        <v>872.0000000000016</v>
+        <v>872</v>
       </c>
       <c r="M31" t="n">
-        <v>872.0000000000016</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="N31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="O31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="P31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="Q31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="R31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="S31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="T31" t="n">
-        <v>673.2315577731808</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="U31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="V31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="W31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="X31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="Y31" t="n">
-        <v>684.2043304114675</v>
+        <v>684.2043304114659</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="C32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="D32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="E32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="F32" t="n">
-        <v>211.3939393939405</v>
+        <v>211.3939393939394</v>
       </c>
       <c r="G32" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="H32" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="I32" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="J32" t="n">
         <v>126.9833246716319</v>
       </c>
       <c r="K32" t="n">
-        <v>342.803324671632</v>
+        <v>342.8033246716321</v>
       </c>
       <c r="L32" t="n">
-        <v>558.6233246716324</v>
+        <v>558.6233246716322</v>
       </c>
       <c r="M32" t="n">
-        <v>427.9365307002925</v>
+        <v>427.936530700291</v>
       </c>
       <c r="N32" t="n">
-        <v>427.9365307002925</v>
+        <v>427.936530700291</v>
       </c>
       <c r="O32" t="n">
-        <v>643.7565307002927</v>
+        <v>643.756530700291</v>
       </c>
       <c r="P32" t="n">
-        <v>859.576530700293</v>
+        <v>859.576530700291</v>
       </c>
       <c r="Q32" t="n">
-        <v>872.000000000002</v>
+        <v>872</v>
       </c>
       <c r="R32" t="n">
-        <v>872.000000000002</v>
+        <v>872</v>
       </c>
       <c r="S32" t="n">
-        <v>872.000000000002</v>
+        <v>872</v>
       </c>
       <c r="T32" t="n">
-        <v>872.000000000002</v>
+        <v>872</v>
       </c>
       <c r="U32" t="n">
-        <v>872.000000000002</v>
+        <v>872</v>
       </c>
       <c r="V32" t="n">
-        <v>651.7979797979815</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="W32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="X32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="Y32" t="n">
-        <v>431.595959595961</v>
+        <v>431.5959595959596</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="C33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="D33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="E33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="F33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="G33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="H33" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="I33" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44</v>
       </c>
       <c r="J33" t="n">
-        <v>83.57482688016826</v>
+        <v>180.6029481041181</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6730951805457</v>
+        <v>223.7012164044955</v>
       </c>
       <c r="L33" t="n">
-        <v>342.4930951805459</v>
+        <v>439.5212164044955</v>
       </c>
       <c r="M33" t="n">
-        <v>352.3636146975988</v>
+        <v>449.3917359215484</v>
       </c>
       <c r="N33" t="n">
-        <v>352.3636146975988</v>
+        <v>498.9831094785365</v>
       </c>
       <c r="O33" t="n">
-        <v>568.1836146975991</v>
+        <v>714.8031094785365</v>
       </c>
       <c r="P33" t="n">
-        <v>784.0036146975993</v>
+        <v>784.0036146975973</v>
       </c>
       <c r="Q33" t="n">
-        <v>872.000000000002</v>
+        <v>872</v>
       </c>
       <c r="R33" t="n">
-        <v>872.000000000002</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="S33" t="n">
-        <v>872.000000000002</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="T33" t="n">
-        <v>651.7979797979815</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="U33" t="n">
-        <v>431.595959595961</v>
+        <v>211.3939393939394</v>
       </c>
       <c r="V33" t="n">
-        <v>400.5690570017215</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="W33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="X33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="Y33" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="C34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="D34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="E34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="F34" t="n">
-        <v>758.4819636689496</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="G34" t="n">
-        <v>675.377041606798</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="H34" t="n">
-        <v>673.2315577731813</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="I34" t="n">
-        <v>681.6688767092642</v>
+        <v>692.6416493475488</v>
       </c>
       <c r="J34" t="n">
-        <v>861.0272273617154</v>
+        <v>872</v>
       </c>
       <c r="K34" t="n">
-        <v>861.0272273617154</v>
+        <v>834.5648749483403</v>
       </c>
       <c r="L34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="M34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="N34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="O34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="P34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="Q34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="R34" t="n">
-        <v>861.0272273617154</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="S34" t="n">
-        <v>861.0272273617154</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="T34" t="n">
-        <v>861.0272273617154</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="U34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="V34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="W34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="X34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="Y34" t="n">
-        <v>872.000000000002</v>
+        <v>684.2043304114659</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>457.8440404040412</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="C35" t="n">
-        <v>237.6420202020205</v>
+        <v>237.6420202020202</v>
       </c>
       <c r="D35" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="E35" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="F35" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="G35" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="H35" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="I35" t="n">
-        <v>17.4399999999996</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="J35" t="n">
-        <v>126.9833246716315</v>
+        <v>126.9833246716319</v>
       </c>
       <c r="K35" t="n">
-        <v>342.8033246716319</v>
+        <v>342.8033246716321</v>
       </c>
       <c r="L35" t="n">
         <v>558.6233246716324</v>
       </c>
       <c r="M35" t="n">
-        <v>436.9817601602044</v>
+        <v>436.9817601602027</v>
       </c>
       <c r="N35" t="n">
-        <v>427.9365307002927</v>
+        <v>427.936530700291</v>
       </c>
       <c r="O35" t="n">
-        <v>643.7565307002931</v>
+        <v>643.756530700291</v>
       </c>
       <c r="P35" t="n">
-        <v>859.5765307002935</v>
+        <v>859.576530700291</v>
       </c>
       <c r="Q35" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R35" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S35" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="T35" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="U35" t="n">
-        <v>651.797979797982</v>
+        <v>872</v>
       </c>
       <c r="V35" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="W35" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="X35" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="Y35" t="n">
-        <v>457.8440404040412</v>
+        <v>457.8440404040404</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>211.3939393939407</v>
+        <v>545.9437999212748</v>
       </c>
       <c r="C36" t="n">
-        <v>211.3939393939407</v>
+        <v>344.8327772490331</v>
       </c>
       <c r="D36" t="n">
-        <v>211.3939393939407</v>
+        <v>344.8327772490331</v>
       </c>
       <c r="E36" t="n">
-        <v>211.3939393939407</v>
+        <v>344.8327772490331</v>
       </c>
       <c r="F36" t="n">
-        <v>211.3939393939407</v>
+        <v>344.8327772490331</v>
       </c>
       <c r="G36" t="n">
-        <v>180.3670367997011</v>
+        <v>180.3670367997012</v>
       </c>
       <c r="H36" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="I36" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44</v>
       </c>
       <c r="J36" t="n">
-        <v>162.4923401007506</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="K36" t="n">
-        <v>205.590608401128</v>
+        <v>60.5382683003774</v>
       </c>
       <c r="L36" t="n">
-        <v>290.1595009577317</v>
+        <v>276.3582683003774</v>
       </c>
       <c r="M36" t="n">
-        <v>300.0300204747846</v>
+        <v>492.1782683003774</v>
       </c>
       <c r="N36" t="n">
-        <v>515.850020474785</v>
+        <v>498.9831094785365</v>
       </c>
       <c r="O36" t="n">
-        <v>693.6364604478184</v>
+        <v>714.8031094785365</v>
       </c>
       <c r="P36" t="n">
-        <v>784.0036146975998</v>
+        <v>784.0036146975973</v>
       </c>
       <c r="Q36" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R36" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S36" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="T36" t="n">
-        <v>651.797979797982</v>
+        <v>872</v>
       </c>
       <c r="U36" t="n">
-        <v>651.797979797982</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="V36" t="n">
-        <v>651.797979797982</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="W36" t="n">
-        <v>431.5959595959613</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="X36" t="n">
-        <v>211.3939393939407</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="Y36" t="n">
-        <v>211.3939393939407</v>
+        <v>545.9437999212748</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="C37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="D37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="E37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="F37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="G37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="H37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="I37" t="n">
-        <v>692.6416493475513</v>
+        <v>692.6416493475488</v>
       </c>
       <c r="J37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="K37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="L37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="M37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="N37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="O37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="P37" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="Q37" t="n">
-        <v>872.0000000000025</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="R37" t="n">
-        <v>673.2315577731817</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="S37" t="n">
-        <v>673.2315577731817</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="T37" t="n">
-        <v>673.2315577731817</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="U37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="V37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="W37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="X37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="Y37" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="C38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="D38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="E38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="F38" t="n">
-        <v>211.3939393939407</v>
+        <v>237.6420202020202</v>
       </c>
       <c r="G38" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="H38" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44</v>
       </c>
       <c r="I38" t="n">
-        <v>17.43999999999994</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="J38" t="n">
-        <v>126.9833246716319</v>
+        <v>126.983324671632</v>
       </c>
       <c r="K38" t="n">
-        <v>342.8033246716321</v>
+        <v>342.8033246716322</v>
       </c>
       <c r="L38" t="n">
-        <v>558.6233246716326</v>
+        <v>558.6233246716325</v>
       </c>
       <c r="M38" t="n">
-        <v>558.6233246716326</v>
+        <v>476.961518667769</v>
       </c>
       <c r="N38" t="n">
-        <v>427.9365307002927</v>
+        <v>427.9365307002909</v>
       </c>
       <c r="O38" t="n">
-        <v>643.7565307002931</v>
+        <v>643.7565307002909</v>
       </c>
       <c r="P38" t="n">
-        <v>859.5765307002935</v>
+        <v>859.576530700291</v>
       </c>
       <c r="Q38" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R38" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S38" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="T38" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="U38" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="V38" t="n">
-        <v>651.797979797982</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="W38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="X38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="Y38" t="n">
-        <v>431.5959595959613</v>
+        <v>431.5959595959596</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="C39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="D39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="E39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="F39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="G39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="H39" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="I39" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44</v>
       </c>
       <c r="J39" t="n">
-        <v>162.4923401007506</v>
+        <v>227.3024346092612</v>
       </c>
       <c r="K39" t="n">
-        <v>293.9052942116636</v>
+        <v>270.4007029096387</v>
       </c>
       <c r="L39" t="n">
-        <v>378.4741867682674</v>
+        <v>415.0937478343322</v>
       </c>
       <c r="M39" t="n">
-        <v>442.0667107414852</v>
+        <v>424.964267351385</v>
       </c>
       <c r="N39" t="n">
-        <v>491.6580842984733</v>
+        <v>474.5556409083732</v>
       </c>
       <c r="O39" t="n">
-        <v>568.1836146975994</v>
+        <v>551.0811713074993</v>
       </c>
       <c r="P39" t="n">
-        <v>784.0036146975998</v>
+        <v>766.9011713074993</v>
       </c>
       <c r="Q39" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R39" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S39" t="n">
-        <v>840.9730974057629</v>
+        <v>678.0460606060605</v>
       </c>
       <c r="T39" t="n">
-        <v>620.7710772037423</v>
+        <v>678.0460606060605</v>
       </c>
       <c r="U39" t="n">
-        <v>400.5690570017217</v>
+        <v>457.8440404040402</v>
       </c>
       <c r="V39" t="n">
-        <v>180.3670367997011</v>
+        <v>237.64202020202</v>
       </c>
       <c r="W39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="X39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="Y39" t="n">
-        <v>180.3670367997011</v>
+        <v>17.43999999999983</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="C40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="D40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="E40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="F40" t="n">
-        <v>686.8331804411752</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="G40" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="H40" t="n">
-        <v>684.2043304114684</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="I40" t="n">
-        <v>692.6416493475513</v>
+        <v>692.6416493475488</v>
       </c>
       <c r="J40" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="K40" t="n">
-        <v>834.5648749483428</v>
+        <v>834.5648749483403</v>
       </c>
       <c r="L40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="M40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="N40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="O40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="P40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="Q40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="R40" t="n">
-        <v>834.5648749483428</v>
+        <v>686.0096949909876</v>
       </c>
       <c r="S40" t="n">
-        <v>834.5648749483428</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="T40" t="n">
-        <v>789.378444133941</v>
+        <v>673.2315577731792</v>
       </c>
       <c r="U40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="V40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="W40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="X40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
       <c r="Y40" t="n">
-        <v>800.3512167722276</v>
+        <v>684.2043304114659</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>457.8440404040411</v>
+        <v>457.8440404040402</v>
       </c>
       <c r="C41" t="n">
-        <v>457.8440404040411</v>
+        <v>237.64202020202</v>
       </c>
       <c r="D41" t="n">
-        <v>237.6420202020205</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="E41" t="n">
-        <v>237.6420202020205</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="F41" t="n">
-        <v>17.43999999999988</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="G41" t="n">
-        <v>17.43999999999988</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="H41" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44</v>
       </c>
       <c r="I41" t="n">
-        <v>17.43999999999988</v>
+        <v>17.44</v>
       </c>
       <c r="J41" t="n">
-        <v>126.9833246716318</v>
+        <v>126.9833246716319</v>
       </c>
       <c r="K41" t="n">
-        <v>342.8033246716322</v>
+        <v>342.8033246716321</v>
       </c>
       <c r="L41" t="n">
-        <v>558.6233246716325</v>
+        <v>558.6233246716324</v>
       </c>
       <c r="M41" t="n">
-        <v>558.6233246716325</v>
+        <v>558.6233246716324</v>
       </c>
       <c r="N41" t="n">
-        <v>427.9365307002922</v>
+        <v>427.9365307002909</v>
       </c>
       <c r="O41" t="n">
-        <v>643.7565307002926</v>
+        <v>643.7565307002909</v>
       </c>
       <c r="P41" t="n">
-        <v>859.5765307002935</v>
+        <v>859.576530700291</v>
       </c>
       <c r="Q41" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R41" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S41" t="n">
-        <v>872.0000000000025</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="T41" t="n">
-        <v>678.0460606060617</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="U41" t="n">
-        <v>678.0460606060617</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="V41" t="n">
-        <v>457.8440404040411</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="W41" t="n">
-        <v>457.8440404040411</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="X41" t="n">
-        <v>457.8440404040411</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="Y41" t="n">
-        <v>457.8440404040411</v>
+        <v>457.8440404040402</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>431.5959595959613</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="C42" t="n">
-        <v>431.5959595959613</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="D42" t="n">
-        <v>237.6420202020204</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="E42" t="n">
-        <v>237.6420202020204</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="F42" t="n">
-        <v>237.6420202020204</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="G42" t="n">
-        <v>237.6420202020204</v>
+        <v>237.6420202020202</v>
       </c>
       <c r="H42" t="n">
-        <v>17.43999999999983</v>
+        <v>17.44</v>
       </c>
       <c r="I42" t="n">
-        <v>17.43999999999983</v>
+        <v>17.44</v>
       </c>
       <c r="J42" t="n">
-        <v>17.43999999999983</v>
+        <v>17.44</v>
       </c>
       <c r="K42" t="n">
-        <v>60.53826830037723</v>
+        <v>224.5400000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>159.957160856981</v>
+        <v>440.3600000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>348.9844696008756</v>
+        <v>440.3600000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>564.804469600876</v>
+        <v>440.3600000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>656.1800000000021</v>
+        <v>656.1800000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="Q42" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R42" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S42" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="T42" t="n">
-        <v>651.797979797982</v>
+        <v>872</v>
       </c>
       <c r="U42" t="n">
-        <v>431.5959595959613</v>
+        <v>872</v>
       </c>
       <c r="V42" t="n">
-        <v>431.5959595959613</v>
+        <v>872</v>
       </c>
       <c r="W42" t="n">
-        <v>431.5959595959613</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="X42" t="n">
-        <v>431.5959595959613</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="Y42" t="n">
-        <v>431.5959595959613</v>
+        <v>457.8440404040404</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
       <c r="C43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
       <c r="D43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
       <c r="E43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
       <c r="F43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
       <c r="G43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
       <c r="H43" t="n">
-        <v>17.43999999999824</v>
+        <v>838.1716493475487</v>
       </c>
       <c r="I43" t="n">
-        <v>17.43999999999824</v>
+        <v>838.1716493475487</v>
       </c>
       <c r="J43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="K43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="L43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="M43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="N43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="O43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="P43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="Q43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="R43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="S43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="T43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="U43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="V43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="W43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="X43" t="n">
-        <v>51.26835065244954</v>
+        <v>872</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.43999999999824</v>
+        <v>872</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="C44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="D44" t="n">
-        <v>431.5959595959613</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="E44" t="n">
-        <v>211.3939393939407</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="F44" t="n">
-        <v>211.3939393939407</v>
+        <v>457.8440404040404</v>
       </c>
       <c r="G44" t="n">
-        <v>17.43999999999983</v>
+        <v>237.6420202020202</v>
       </c>
       <c r="H44" t="n">
-        <v>17.43999999999983</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="I44" t="n">
-        <v>17.43999999999983</v>
+        <v>17.44</v>
       </c>
       <c r="J44" t="n">
-        <v>126.9833246716318</v>
+        <v>126.9833246716319</v>
       </c>
       <c r="K44" t="n">
-        <v>342.8033246716317</v>
+        <v>342.8033246716319</v>
       </c>
       <c r="L44" t="n">
-        <v>558.623324671632</v>
+        <v>558.6233246716318</v>
       </c>
       <c r="M44" t="n">
-        <v>427.9365307002927</v>
+        <v>558.6233246716318</v>
       </c>
       <c r="N44" t="n">
-        <v>427.9365307002927</v>
+        <v>427.936530700291</v>
       </c>
       <c r="O44" t="n">
-        <v>643.7565307002931</v>
+        <v>643.756530700291</v>
       </c>
       <c r="P44" t="n">
-        <v>859.5765307002935</v>
+        <v>859.576530700291</v>
       </c>
       <c r="Q44" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="R44" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="S44" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="T44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="U44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="V44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="W44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="X44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
       <c r="Y44" t="n">
-        <v>651.797979797982</v>
+        <v>678.0460606060606</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="C45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="D45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="E45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="F45" t="n">
-        <v>645.2220364444729</v>
+        <v>431.5959595959596</v>
       </c>
       <c r="G45" t="n">
-        <v>425.0200162424524</v>
+        <v>211.3939393939394</v>
       </c>
       <c r="H45" t="n">
-        <v>204.8179960404317</v>
+        <v>17.44000000000005</v>
       </c>
       <c r="I45" t="n">
-        <v>17.4399999999996</v>
+        <v>17.44</v>
       </c>
       <c r="J45" t="n">
-        <v>227.3024346092608</v>
+        <v>227.3024346092612</v>
       </c>
       <c r="K45" t="n">
-        <v>270.4007029096383</v>
+        <v>371.1594947809392</v>
       </c>
       <c r="L45" t="n">
-        <v>486.2207029096386</v>
+        <v>586.9794947809391</v>
       </c>
       <c r="M45" t="n">
-        <v>702.0407029096391</v>
+        <v>586.9794947809391</v>
       </c>
       <c r="N45" t="n">
-        <v>702.0407029096391</v>
+        <v>586.9794947809391</v>
       </c>
       <c r="O45" t="n">
-        <v>802.7994947809417</v>
+        <v>802.7994947809392</v>
       </c>
       <c r="P45" t="n">
-        <v>872.0000000000025</v>
+        <v>872</v>
       </c>
       <c r="Q45" t="n">
-        <v>865.4240566464935</v>
+        <v>872</v>
       </c>
       <c r="R45" t="n">
-        <v>865.4240566464935</v>
+        <v>872</v>
       </c>
       <c r="S45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="T45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="U45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="V45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="W45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="X45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
       <c r="Y45" t="n">
-        <v>645.2220364444729</v>
+        <v>651.7979797979798</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="C46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="D46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="E46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="F46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="G46" t="n">
-        <v>17.43999999999824</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="H46" t="n">
-        <v>17.43999999999824</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="I46" t="n">
-        <v>17.43999999999824</v>
+        <v>17.43999999999983</v>
       </c>
       <c r="J46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="K46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="L46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="M46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="N46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="O46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="P46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="Q46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="R46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="S46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="T46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="U46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="V46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="W46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="X46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.41835065244955</v>
+        <v>36.41835065245114</v>
       </c>
     </row>
   </sheetData>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>242.8451879438248</v>
+        <v>168.2878906160782</v>
       </c>
       <c r="N2" t="n">
-        <v>96.39747983756659</v>
+        <v>170.9547771653126</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -8046,10 +8046,10 @@
         <v>15.48248474671647</v>
       </c>
       <c r="K3" t="n">
-        <v>38.16397366056371</v>
+        <v>203.4663956561844</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.399062449706449</v>
       </c>
       <c r="M3" t="n">
         <v>399.0297782656032</v>
@@ -8058,7 +8058,7 @@
         <v>358.9077034777898</v>
       </c>
       <c r="O3" t="n">
-        <v>169.7014844453271</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -8210,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>242.8451879438248</v>
+        <v>168.2878906160786</v>
       </c>
       <c r="N5" t="n">
-        <v>96.39747983756659</v>
+        <v>170.9547771653126</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8280,10 +8280,10 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>46.24744307388079</v>
+        <v>15.48248474671647</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>203.4663956561844</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
         <v>399.0297782656032</v>
       </c>
       <c r="N6" t="n">
-        <v>358.9077034777898</v>
+        <v>186.2062661487697</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>242.8451879438248</v>
+        <v>168.2878906160782</v>
       </c>
       <c r="N8" t="n">
-        <v>96.39747983756659</v>
+        <v>170.9547771653126</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>15.48248474671647</v>
+        <v>223.3479428526074</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -8526,16 +8526,16 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>260.0932521474404</v>
+        <v>399.0297782656032</v>
       </c>
       <c r="N9" t="n">
         <v>358.9077034777898</v>
       </c>
       <c r="O9" t="n">
-        <v>169.7014844453271</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>177.1004997787264</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>168.2878906160788</v>
+        <v>0.2878906160789398</v>
       </c>
       <c r="N11" t="n">
-        <v>2.954777165312578</v>
+        <v>170.9547771653126</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8754,16 +8754,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>15.48248474671647</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6.868784230078072</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>152.0297782656032</v>
+        <v>143.4160777489646</v>
       </c>
       <c r="N12" t="n">
         <v>111.9077034777898</v>
@@ -8921,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>74.84518794382484</v>
+        <v>153.738317247247</v>
       </c>
       <c r="N14" t="n">
-        <v>96.39747983756671</v>
+        <v>170.9547771653126</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9000,19 +9000,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>152.0297782656032</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>109.6759879291422</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>9.10049977872643</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2878906160785135</v>
+        <v>168.2878906160786</v>
       </c>
       <c r="N17" t="n">
-        <v>170.9547771653126</v>
+        <v>2.954777165312578</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9228,7 +9228,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>94.48248474671647</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>176.1737578392147</v>
+        <v>55.31557797023856</v>
       </c>
       <c r="N18" t="n">
         <v>111.9077034777898</v>
@@ -9246,10 +9246,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>9.10049977872643</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9395,10 +9395,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>168.2878906160789</v>
+        <v>153.738317247247</v>
       </c>
       <c r="N20" t="n">
-        <v>2.954777165312578</v>
+        <v>170.9547771653126</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>288.0814613170041</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -9632,10 +9632,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>168.2878906160789</v>
+        <v>74.84518794382484</v>
       </c>
       <c r="N23" t="n">
-        <v>2.954777165312578</v>
+        <v>96.39747983756659</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9702,28 +9702,28 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J24" t="n">
-        <v>168.163759146915</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>67.2581506056494</v>
       </c>
       <c r="M24" t="n">
-        <v>8.009998692299316</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>111.9077034777898</v>
+        <v>33.84663092249433</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>169.7014844453271</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -9857,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>84.48105656829742</v>
+        <v>57.5496125923945</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>137.4200390775107</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>137.4200390775098</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9939,28 +9939,28 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>15.48248474671647</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>132.5768762054507</v>
+        <v>58.84064137759276</v>
       </c>
       <c r="M27" t="n">
-        <v>45.53586334749651</v>
+        <v>152.0297782656032</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>50.55997501136488</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>113.4652619121979</v>
+        <v>114.6916235561093</v>
       </c>
       <c r="N29" t="n">
-        <v>8.954777165312578</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10182,16 +10182,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>132.5768762054507</v>
       </c>
       <c r="M30" t="n">
-        <v>202.3651507445495</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>84.29728103682382</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>59.25775426859219</v>
+        <v>113.4652619121971</v>
       </c>
       <c r="N32" t="n">
-        <v>170.9547771653126</v>
+        <v>107.0029700021042</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>18.29354343774489</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -10656,16 +10656,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>62.16167225653719</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>370.0297782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>329.9077034777902</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>102.2837470443509</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>80.84518794382484</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>41.57485113368602</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10887,16 +10887,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>39.35101347209168</v>
       </c>
       <c r="M39" t="n">
-        <v>54.26465096582318</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -10905,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>148.1004997787268</v>
+        <v>148.1004997787264</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>229.9557407076439</v>
       </c>
       <c r="N41" t="n">
-        <v>26.57485113368568</v>
+        <v>26.57485113368449</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11127,22 +11127,22 @@
         <v>15.48248474671647</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>165.6583148481037</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>117.5768762054507</v>
       </c>
       <c r="M42" t="n">
-        <v>342.9664537644866</v>
+        <v>152.0297782656032</v>
       </c>
       <c r="N42" t="n">
-        <v>329.9077034777902</v>
+        <v>111.9077034777898</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>125.7014844453271</v>
       </c>
       <c r="P42" t="n">
-        <v>148.1004997787268</v>
+        <v>148.1004997787264</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>113.465261912199</v>
+        <v>242.8451879438248</v>
       </c>
       <c r="N44" t="n">
-        <v>170.9547771653126</v>
+        <v>41.57485113368517</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11364,19 +11364,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>101.7765574457581</v>
       </c>
       <c r="L45" t="n">
-        <v>132.5768762054511</v>
+        <v>132.5768762054507</v>
       </c>
       <c r="M45" t="n">
-        <v>370.0297782656036</v>
+        <v>152.0297782656032</v>
       </c>
       <c r="N45" t="n">
         <v>111.9077034777898</v>
       </c>
       <c r="O45" t="n">
-        <v>24.47804189108736</v>
+        <v>140.7014844453271</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -22515,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299369</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10.33915573984956</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -22566,16 +22566,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>179.161240020021</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.083969915444612</v>
+        <v>249.0839699154446</v>
       </c>
       <c r="V2" t="n">
-        <v>151.6090293754352</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809473</v>
+        <v>30.37657101093342</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606675</v>
@@ -22597,7 +22597,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>100.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -22606,7 +22606,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>77.82108304483864</v>
+        <v>324.8210830448386</v>
       </c>
       <c r="H3" t="n">
         <v>323.2977664317041</v>
@@ -22639,16 +22639,16 @@
         <v>55.83956697727202</v>
       </c>
       <c r="R3" t="n">
-        <v>490.2491557829453</v>
+        <v>243.2491557829453</v>
       </c>
       <c r="S3" t="n">
-        <v>231.9465414740454</v>
+        <v>202.5041414740453</v>
       </c>
       <c r="T3" t="n">
-        <v>154.6557557835516</v>
+        <v>401.6557557835516</v>
       </c>
       <c r="U3" t="n">
-        <v>400.1499352318849</v>
+        <v>182.5923352318848</v>
       </c>
       <c r="V3" t="n">
         <v>414.5106671915202</v>
@@ -22657,7 +22657,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X3" t="n">
-        <v>172.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -22679,19 +22679,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>244.27387284153</v>
       </c>
       <c r="H4" t="n">
-        <v>26.59772886461892</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>153.4774556201183</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -22706,10 +22706,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>53.35407527168462</v>
+        <v>34.56550812575782</v>
       </c>
       <c r="O4" t="n">
-        <v>131.6095640790147</v>
+        <v>531.6095640790149</v>
       </c>
       <c r="P4" t="n">
         <v>194.3198973282773</v>
@@ -22718,13 +22718,13 @@
         <v>261.3622664255978</v>
       </c>
       <c r="R4" t="n">
-        <v>273.1915608352241</v>
+        <v>291.9801279811509</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>348.9544797028555</v>
       </c>
       <c r="T4" t="n">
-        <v>206.7345665062577</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>150.9163912744579</v>
@@ -22733,10 +22733,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>189.0232709658304</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -22752,19 +22752,19 @@
         <v>81.9993129555744</v>
       </c>
       <c r="C5" t="n">
-        <v>49.4745782429938</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984967</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868534</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.040789372443233</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22797,7 +22797,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>14.28392289738281</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>55.73153463649363</v>
@@ -22806,7 +22806,7 @@
         <v>179.1612400200211</v>
       </c>
       <c r="U5" t="n">
-        <v>2.083969915444726</v>
+        <v>249.0839699154447</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668238</v>
@@ -22828,7 +22828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>137.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -22837,16 +22837,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>95.67209722191262</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>77.82108304483864</v>
+        <v>324.8210830448386</v>
       </c>
       <c r="H6" t="n">
-        <v>105.7401664317042</v>
+        <v>323.2977664317041</v>
       </c>
       <c r="I6" t="n">
         <v>185.5042160800278</v>
@@ -22888,7 +22888,7 @@
         <v>400.1499352318849</v>
       </c>
       <c r="V6" t="n">
-        <v>167.5106671915202</v>
+        <v>196.9530671915201</v>
       </c>
       <c r="W6" t="n">
         <v>432.3731429098285</v>
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>171.1483414464339</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -22919,13 +22919,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>37.29932828268113</v>
       </c>
       <c r="G7" t="n">
-        <v>244.27387284153</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>221.9251261016186</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22943,7 +22943,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>53.35407527168474</v>
+        <v>34.56550812575794</v>
       </c>
       <c r="O7" t="n">
         <v>131.6095640790148</v>
@@ -22955,7 +22955,7 @@
         <v>261.3622664255979</v>
       </c>
       <c r="R7" t="n">
-        <v>273.1915608352242</v>
+        <v>291.980127981151</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,28 +22986,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>81.99931295557428</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>49.47457824299369</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>10.33915573984956</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4.36328960686842</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>155.0407893724433</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>83.90259686861427</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23034,28 +23034,28 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>143.0492973207568</v>
       </c>
       <c r="S8" t="n">
-        <v>55.73153463649375</v>
+        <v>55.73153463649352</v>
       </c>
       <c r="T8" t="n">
-        <v>179.1612400200212</v>
+        <v>179.161240020021</v>
       </c>
       <c r="U8" t="n">
-        <v>249.0839699154448</v>
+        <v>2.083969915444612</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>12.29342416682377</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>24.19881170366179</v>
+        <v>192.2818334606675</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>111.3174326828062</v>
       </c>
     </row>
     <row r="9">
@@ -23065,7 +23065,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.9989566463265</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -23080,10 +23080,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>324.8210830448386</v>
+        <v>77.82108304483864</v>
       </c>
       <c r="H9" t="n">
-        <v>323.2977664317041</v>
+        <v>105.7401664317042</v>
       </c>
       <c r="I9" t="n">
         <v>185.5042160800278</v>
@@ -23122,19 +23122,19 @@
         <v>154.6557557835516</v>
       </c>
       <c r="U9" t="n">
-        <v>400.1499352318849</v>
+        <v>0.1499352318846335</v>
       </c>
       <c r="V9" t="n">
-        <v>414.5106671915202</v>
+        <v>167.5106671915202</v>
       </c>
       <c r="W9" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>172.8627394453875</v>
+        <v>19.86273944538732</v>
       </c>
       <c r="Y9" t="n">
-        <v>152.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -23165,13 +23165,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>153.4774556201183</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>199.0607738011431</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23180,19 +23180,19 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>34.56550812575805</v>
+        <v>53.35407527168462</v>
       </c>
       <c r="O10" t="n">
-        <v>131.6095640790149</v>
+        <v>131.6095640790147</v>
       </c>
       <c r="P10" t="n">
-        <v>194.3198973282775</v>
+        <v>194.3198973282773</v>
       </c>
       <c r="Q10" t="n">
-        <v>261.362266425598</v>
+        <v>242.573699279671</v>
       </c>
       <c r="R10" t="n">
-        <v>291.9801279811511</v>
+        <v>291.9801279811509</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23204,16 +23204,16 @@
         <v>150.9163912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>203.1832651574545</v>
+        <v>71.40301022381655</v>
       </c>
     </row>
     <row r="11">
@@ -23311,13 +23311,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>174.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>171.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>134.1659785941768</v>
+        <v>156.8210830448387</v>
       </c>
       <c r="H12" t="n">
         <v>155.2977664317042</v>
@@ -23353,10 +23353,10 @@
         <v>322.2491557829453</v>
       </c>
       <c r="S12" t="n">
-        <v>281.5041414740453</v>
+        <v>34.5041414740453</v>
       </c>
       <c r="T12" t="n">
-        <v>233.6557557835515</v>
+        <v>111.6923117731001</v>
       </c>
       <c r="U12" t="n">
         <v>232.1499352318849</v>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>313.9993129555745</v>
+        <v>66.99931295557451</v>
       </c>
       <c r="C14" t="n">
         <v>281.4745782429939</v>
@@ -23469,16 +23469,16 @@
         <v>242.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>218.165811616982</v>
+        <v>236.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>6.372818080455346</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>222.4297039296581</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23517,13 +23517,13 @@
         <v>411.1612400200212</v>
       </c>
       <c r="U14" t="n">
-        <v>481.0839699154448</v>
+        <v>234.0839699154448</v>
       </c>
       <c r="V14" t="n">
         <v>461.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>223.3734759809475</v>
+        <v>470.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>424.2818334606677</v>
@@ -23539,13 +23539,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>216.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>193.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>179.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>174.6720972219126</v>
@@ -23590,19 +23590,19 @@
         <v>322.2491557829453</v>
       </c>
       <c r="S15" t="n">
-        <v>281.5041414740453</v>
+        <v>34.5041414740453</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7587582069564007</v>
+        <v>111.6923117731001</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>232.1499352318849</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>246.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>17.37314290982852</v>
+        <v>264.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>251.8627394453875</v>
@@ -23630,13 +23630,13 @@
         <v>112.9809048369565</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>106.3828559677419</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>76.27387284153004</v>
       </c>
       <c r="H16" t="n">
-        <v>22.1592971063378</v>
+        <v>53.92512610161862</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>141.0696281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>231.9306114025499</v>
+        <v>17.50805359799728</v>
       </c>
       <c r="N16" t="n">
         <v>285.3540752716848</v>
@@ -23779,10 +23779,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>193.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>164.0865787759141</v>
       </c>
       <c r="E18" t="n">
         <v>174.6720972219126</v>
@@ -23824,7 +23824,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>322.2491557829453</v>
+        <v>75.24915578294531</v>
       </c>
       <c r="S18" t="n">
         <v>281.5041414740453</v>
@@ -23836,10 +23836,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>109.6971584129535</v>
+        <v>246.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>264.3731429098285</v>
+        <v>17.37314290982852</v>
       </c>
       <c r="X18" t="n">
         <v>251.8627394453875</v>
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66.99931295557451</v>
+        <v>313.9993129555745</v>
       </c>
       <c r="C20" t="n">
         <v>34.47457824299391</v>
@@ -23946,13 +23946,13 @@
         <v>236.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>236.8896287080119</v>
+        <v>228.8025220101134</v>
       </c>
       <c r="G20" t="n">
-        <v>234.0407893724434</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>222.4297039296581</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23991,13 +23991,13 @@
         <v>411.1612400200212</v>
       </c>
       <c r="U20" t="n">
-        <v>481.0839699154448</v>
+        <v>234.0839699154448</v>
       </c>
       <c r="V20" t="n">
-        <v>244.293424166824</v>
+        <v>461.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>223.3734759809475</v>
+        <v>470.3734759809475</v>
       </c>
       <c r="X20" t="n">
         <v>424.2818334606677</v>
@@ -24013,13 +24013,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>216.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>193.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>179.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>174.6720972219126</v>
@@ -24067,13 +24067,13 @@
         <v>34.5041414740453</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>111.6923117731002</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>232.1499352318849</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7587582069565997</v>
+        <v>246.5106671915202</v>
       </c>
       <c r="W21" t="n">
         <v>264.3731429098285</v>
@@ -24101,7 +24101,7 @@
         <v>117.5362180555555</v>
       </c>
       <c r="E22" t="n">
-        <v>112.9809048369565</v>
+        <v>70.68874899132612</v>
       </c>
       <c r="F22" t="n">
         <v>106.3828559677419</v>
@@ -24119,13 +24119,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>31.06077380114307</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>141.0696281577792</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>17.50805359799728</v>
+        <v>231.9306114025499</v>
       </c>
       <c r="N22" t="n">
         <v>285.3540752716848</v>
@@ -24180,16 +24180,16 @@
         <v>242.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>218.165811616982</v>
+        <v>236.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>236.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>234.0407893724434</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>222.4297039296581</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24225,7 +24225,7 @@
         <v>287.7315346364937</v>
       </c>
       <c r="T23" t="n">
-        <v>411.1612400200212</v>
+        <v>164.1612400200212</v>
       </c>
       <c r="U23" t="n">
         <v>481.0839699154448</v>
@@ -24234,13 +24234,13 @@
         <v>461.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>470.3734759809475</v>
+        <v>223.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>424.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>343.3174326828064</v>
+        <v>125.7598326828065</v>
       </c>
     </row>
     <row r="24">
@@ -24250,7 +24250,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>216.5565566463266</v>
       </c>
       <c r="C24" t="n">
         <v>193.0999124455193</v>
@@ -24265,13 +24265,13 @@
         <v>171.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>52.66917075258318</v>
+        <v>156.8210830448387</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>155.2977664317042</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>17.50421608002777</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24301,25 +24301,25 @@
         <v>322.2491557829453</v>
       </c>
       <c r="S24" t="n">
-        <v>281.5041414740453</v>
+        <v>34.5041414740453</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>233.6557557835515</v>
       </c>
       <c r="U24" t="n">
-        <v>232.1499352318849</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>246.5106671915202</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="W24" t="n">
-        <v>264.3731429098285</v>
+        <v>31.47614533323349</v>
       </c>
       <c r="X24" t="n">
         <v>251.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>231.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -24356,10 +24356,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>31.06077380114307</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>141.0696281577792</v>
       </c>
       <c r="M25" t="n">
         <v>231.9306114025499</v>
@@ -24380,16 +24380,16 @@
         <v>523.9801279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>180.9544797028555</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>38.73456650625771</v>
+        <v>22.01013331646429</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>31.17031021621619</v>
+        <v>14.42666530431242</v>
       </c>
       <c r="W25" t="n">
         <v>58.37280983870968</v>
@@ -24398,7 +24398,7 @@
         <v>79.44364543010755</v>
       </c>
       <c r="Y25" t="n">
-        <v>77.17319700383194</v>
+        <v>119.4653528494624</v>
       </c>
     </row>
     <row r="26">
@@ -24411,10 +24411,10 @@
         <v>334.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>84.47457824299391</v>
+        <v>302.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>263.3391557398498</v>
+        <v>263.3391557398514</v>
       </c>
       <c r="E26" t="n">
         <v>257.3632896068686</v>
@@ -24465,19 +24465,19 @@
         <v>432.1612400200212</v>
       </c>
       <c r="U26" t="n">
-        <v>502.0839699154448</v>
+        <v>284.0839699154448</v>
       </c>
       <c r="V26" t="n">
         <v>482.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>299.3590759809456</v>
+        <v>273.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>445.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>146.3174326828064</v>
+        <v>172.3030326828051</v>
       </c>
     </row>
     <row r="27">
@@ -24496,16 +24496,16 @@
         <v>200.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>179.9554636536164</v>
       </c>
       <c r="F27" t="n">
         <v>192.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>177.8210830448387</v>
       </c>
       <c r="H27" t="n">
-        <v>139.7765466984541</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>38.50421608002777</v>
@@ -24535,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>125.2491557829453</v>
+        <v>343.2491557829453</v>
       </c>
       <c r="S27" t="n">
         <v>302.5041414740453</v>
@@ -24550,13 +24550,13 @@
         <v>267.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>285.3731429098285</v>
+        <v>67.37314290982852</v>
       </c>
       <c r="X27" t="n">
         <v>272.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>252.3913927661343</v>
+        <v>34.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -24605,7 +24605,7 @@
         <v>306.3540752716848</v>
       </c>
       <c r="O28" t="n">
-        <v>221.7462969330881</v>
+        <v>384.6095640790149</v>
       </c>
       <c r="P28" t="n">
         <v>447.3198973282775</v>
@@ -24632,10 +24632,10 @@
         <v>79.37280983870968</v>
       </c>
       <c r="X28" t="n">
-        <v>100.4436454301076</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>140.4653528494624</v>
+        <v>78.04573113364314</v>
       </c>
     </row>
     <row r="29">
@@ -24648,10 +24648,10 @@
         <v>319.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>95.46017824299153</v>
+        <v>69.47457824299391</v>
       </c>
       <c r="D29" t="n">
-        <v>248.339155739851</v>
+        <v>30.33915573984979</v>
       </c>
       <c r="E29" t="n">
         <v>242.3632896068686</v>
@@ -24699,22 +24699,22 @@
         <v>293.7315346364937</v>
       </c>
       <c r="T29" t="n">
-        <v>199.161240020021</v>
+        <v>417.1612400200212</v>
       </c>
       <c r="U29" t="n">
-        <v>269.0839699154446</v>
+        <v>487.0839699154448</v>
       </c>
       <c r="V29" t="n">
         <v>467.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>476.3734759809475</v>
+        <v>284.3590759809475</v>
       </c>
       <c r="X29" t="n">
         <v>430.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>131.3174326828062</v>
+        <v>131.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -24724,7 +24724,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.556556646326442</v>
+        <v>222.5565566463266</v>
       </c>
       <c r="C30" t="n">
         <v>199.0999124455193</v>
@@ -24736,16 +24736,16 @@
         <v>180.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>115.2449078944461</v>
+        <v>177.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>162.8210830448387</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>23.50421608002777</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24775,25 +24775,25 @@
         <v>328.2491557829453</v>
       </c>
       <c r="S30" t="n">
-        <v>287.5041414740453</v>
+        <v>69.5041414740453</v>
       </c>
       <c r="T30" t="n">
-        <v>21.65575578355137</v>
+        <v>239.6557557835515</v>
       </c>
       <c r="U30" t="n">
-        <v>238.1499352318849</v>
+        <v>207.433301663589</v>
       </c>
       <c r="V30" t="n">
         <v>252.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>270.3731429098285</v>
+        <v>52.37314290982852</v>
       </c>
       <c r="X30" t="n">
         <v>257.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>237.3913927661343</v>
+        <v>19.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -24836,10 +24836,10 @@
         <v>147.0696281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>237.9306114025499</v>
+        <v>41.14985359799738</v>
       </c>
       <c r="N31" t="n">
-        <v>94.57331746713231</v>
+        <v>291.3540752716848</v>
       </c>
       <c r="O31" t="n">
         <v>369.6095640790149</v>
@@ -24894,10 +24894,10 @@
         <v>242.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>24.88962870801157</v>
+        <v>24.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>48.0263893724422</v>
+        <v>48.02638937244339</v>
       </c>
       <c r="H32" t="n">
         <v>228.4297039296581</v>
@@ -24942,10 +24942,10 @@
         <v>487.0839699154448</v>
       </c>
       <c r="V32" t="n">
-        <v>249.8510241668236</v>
+        <v>249.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>258.3734759809473</v>
+        <v>258.3734759809475</v>
       </c>
       <c r="X32" t="n">
         <v>430.2818334606677</v>
@@ -24979,7 +24979,7 @@
         <v>162.8210830448387</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>161.2977664317042</v>
       </c>
       <c r="I33" t="n">
         <v>23.50421608002777</v>
@@ -25009,22 +25009,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>328.2491557829453</v>
+        <v>110.2491557829453</v>
       </c>
       <c r="S33" t="n">
-        <v>287.5041414740453</v>
+        <v>69.5041414740453</v>
       </c>
       <c r="T33" t="n">
-        <v>21.65575578355126</v>
+        <v>239.6557557835515</v>
       </c>
       <c r="U33" t="n">
-        <v>20.14993523188457</v>
+        <v>20.14993523188485</v>
       </c>
       <c r="V33" t="n">
-        <v>221.7940336232231</v>
+        <v>60.49626719152002</v>
       </c>
       <c r="W33" t="n">
-        <v>52.37314290982823</v>
+        <v>270.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>257.8627394453875</v>
@@ -25052,13 +25052,13 @@
         <v>118.9809048369565</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>112.3828559677419</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>82.27387284153004</v>
       </c>
       <c r="H34" t="n">
-        <v>57.80109710633808</v>
+        <v>59.92512610161862</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25067,10 +25067,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>37.06077380114307</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>147.0696281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>237.9306114025499</v>
@@ -25091,7 +25091,7 @@
         <v>529.9801279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>186.9544797028555</v>
+        <v>174.3041238572252</v>
       </c>
       <c r="T34" t="n">
         <v>44.73456650625771</v>
@@ -25122,10 +25122,10 @@
         <v>319.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>69.47457824299352</v>
+        <v>69.47457824299391</v>
       </c>
       <c r="D35" t="n">
-        <v>30.33915573984939</v>
+        <v>30.33915573984979</v>
       </c>
       <c r="E35" t="n">
         <v>242.3632896068686</v>
@@ -25176,10 +25176,10 @@
         <v>417.1612400200212</v>
       </c>
       <c r="U35" t="n">
-        <v>269.0839699154444</v>
+        <v>487.0839699154448</v>
       </c>
       <c r="V35" t="n">
-        <v>467.8510241668239</v>
+        <v>275.8366241668239</v>
       </c>
       <c r="W35" t="n">
         <v>476.3734759809475</v>
@@ -25188,7 +25188,7 @@
         <v>430.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>157.303032682805</v>
+        <v>131.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -25201,7 +25201,7 @@
         <v>222.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>199.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>185.9376868977026</v>
@@ -25213,7 +25213,7 @@
         <v>177.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>132.1044494765414</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25252,22 +25252,22 @@
         <v>287.5041414740453</v>
       </c>
       <c r="T36" t="n">
-        <v>21.65575578355114</v>
+        <v>239.6557557835515</v>
       </c>
       <c r="U36" t="n">
-        <v>238.1499352318849</v>
+        <v>20.14993523188485</v>
       </c>
       <c r="V36" t="n">
         <v>252.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>52.37314290982812</v>
+        <v>270.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>39.86273944538715</v>
+        <v>257.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>237.3913927661343</v>
+        <v>132.5957546881965</v>
       </c>
     </row>
     <row r="37">
@@ -25322,10 +25322,10 @@
         <v>432.3198973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>499.362266425598</v>
+        <v>302.5815086210455</v>
       </c>
       <c r="R37" t="n">
-        <v>333.1993701765986</v>
+        <v>529.9801279811511</v>
       </c>
       <c r="S37" t="n">
         <v>186.9544797028555</v>
@@ -25368,10 +25368,10 @@
         <v>242.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>24.88962870801146</v>
+        <v>50.87522870801189</v>
       </c>
       <c r="G38" t="n">
-        <v>48.02638937244197</v>
+        <v>22.04078937244336</v>
       </c>
       <c r="H38" t="n">
         <v>228.4297039296581</v>
@@ -25416,10 +25416,10 @@
         <v>487.0839699154448</v>
       </c>
       <c r="V38" t="n">
-        <v>249.8510241668235</v>
+        <v>249.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>258.3734759809471</v>
+        <v>258.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>430.2818334606677</v>
@@ -25453,7 +25453,7 @@
         <v>162.8210830448387</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>161.2977664317042</v>
       </c>
       <c r="I39" t="n">
         <v>23.50421608002777</v>
@@ -25486,19 +25486,19 @@
         <v>328.2491557829453</v>
       </c>
       <c r="S39" t="n">
-        <v>256.7875079057481</v>
+        <v>95.48974147404516</v>
       </c>
       <c r="T39" t="n">
-        <v>21.65575578355114</v>
+        <v>239.6557557835515</v>
       </c>
       <c r="U39" t="n">
-        <v>20.14993523188446</v>
+        <v>20.14993523188485</v>
       </c>
       <c r="V39" t="n">
-        <v>34.51066719151976</v>
+        <v>34.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>270.3731429098285</v>
+        <v>52.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>257.8627394453875</v>
@@ -25526,10 +25526,10 @@
         <v>118.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>112.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>79.67131131212034</v>
+        <v>82.27387284153004</v>
       </c>
       <c r="H40" t="n">
         <v>59.92512610161862</v>
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>147.0696281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>237.9306114025499</v>
@@ -25565,10 +25565,10 @@
         <v>529.9801279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>186.9544797028555</v>
+        <v>174.3041238572252</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>44.73456650625771</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -25596,16 +25596,16 @@
         <v>466.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>434.4745782429939</v>
+        <v>216.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>177.3391557398494</v>
+        <v>177.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>389.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>171.8896287080115</v>
+        <v>389.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>387.0407893724433</v>
@@ -25644,16 +25644,16 @@
         <v>128.0492973207568</v>
       </c>
       <c r="S41" t="n">
-        <v>440.7315346364937</v>
+        <v>222.7315346364937</v>
       </c>
       <c r="T41" t="n">
-        <v>372.1468400200198</v>
+        <v>564.1612400200212</v>
       </c>
       <c r="U41" t="n">
         <v>634.0839699154449</v>
       </c>
       <c r="V41" t="n">
-        <v>396.8510241668235</v>
+        <v>614.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>623.3734759809475</v>
@@ -25662,7 +25662,7 @@
         <v>577.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>496.3174326828064</v>
+        <v>304.3030326828062</v>
       </c>
     </row>
     <row r="42">
@@ -25678,7 +25678,7 @@
         <v>346.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>140.9232868977011</v>
+        <v>332.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>327.6720972219126</v>
@@ -25687,10 +25687,10 @@
         <v>324.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>309.8210830448386</v>
+        <v>91.82108304483864</v>
       </c>
       <c r="H42" t="n">
-        <v>90.29776643170374</v>
+        <v>90.29776643170413</v>
       </c>
       <c r="I42" t="n">
         <v>170.5042160800278</v>
@@ -25726,19 +25726,19 @@
         <v>434.5041414740453</v>
       </c>
       <c r="T42" t="n">
-        <v>168.6557557835512</v>
+        <v>386.6557557835516</v>
       </c>
       <c r="U42" t="n">
-        <v>167.1499352318845</v>
+        <v>385.1499352318849</v>
       </c>
       <c r="V42" t="n">
         <v>399.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>417.3731429098285</v>
+        <v>199.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>404.8627394453875</v>
+        <v>212.8483394453876</v>
       </c>
       <c r="Y42" t="n">
         <v>384.3913927661343</v>
@@ -25769,7 +25769,7 @@
         <v>229.27387284153</v>
       </c>
       <c r="H43" t="n">
-        <v>206.9251261016186</v>
+        <v>173.4350589556919</v>
       </c>
       <c r="I43" t="n">
         <v>138.4774556201183</v>
@@ -25820,7 +25820,7 @@
         <v>232.4436454301076</v>
       </c>
       <c r="Y43" t="n">
-        <v>238.9752857035356</v>
+        <v>272.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -25836,19 +25836,19 @@
         <v>449.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>192.3391557398494</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>186.3632896068682</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>404.8896287080119</v>
+        <v>186.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>210.0263893724418</v>
+        <v>184.0407893724433</v>
       </c>
       <c r="H44" t="n">
-        <v>390.429703929658</v>
+        <v>172.429703929658</v>
       </c>
       <c r="I44" t="n">
         <v>83.90259686861427</v>
@@ -25884,7 +25884,7 @@
         <v>455.7315346364937</v>
       </c>
       <c r="T44" t="n">
-        <v>361.1612400200208</v>
+        <v>387.1468400200212</v>
       </c>
       <c r="U44" t="n">
         <v>649.0839699154449</v>
@@ -25921,16 +25921,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>121.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>106.8210830448382</v>
+        <v>106.8210830448386</v>
       </c>
       <c r="H45" t="n">
-        <v>105.2977664317037</v>
+        <v>131.2833664317042</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>185.5042160800278</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,13 +25954,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>49.32938305729807</v>
+        <v>55.83956697727202</v>
       </c>
       <c r="R45" t="n">
         <v>490.2491557829453</v>
       </c>
       <c r="S45" t="n">
-        <v>231.5041414740449</v>
+        <v>231.5041414740453</v>
       </c>
       <c r="T45" t="n">
         <v>401.6557557835516</v>
@@ -26003,10 +26003,10 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>225.4853056956032</v>
+        <v>244.27387284153</v>
       </c>
       <c r="H46" t="n">
-        <v>221.9251261016186</v>
+        <v>203.1365589556918</v>
       </c>
       <c r="I46" t="n">
         <v>153.4774556201183</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>860907.7361651395</v>
+        <v>860907.7361651391</v>
       </c>
     </row>
     <row r="3">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2411682.519975296</v>
+        <v>2411682.519975297</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3698799.644539613</v>
+        <v>3698799.644539615</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4363229.145041021</v>
+        <v>4363229.145041023</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5027658.645542429</v>
+        <v>5027658.645542433</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5692088.146043837</v>
+        <v>5692088.146043839</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6302201.923522099</v>
+        <v>6302201.923522101</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6938018.028390071</v>
+        <v>6938018.02839007</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7578703.226331471</v>
+        <v>7578703.226331469</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8219388.42427287</v>
+        <v>8219388.424272868</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8860073.622214269</v>
+        <v>8860073.622214263</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9226861.830774447</v>
+        <v>9226861.830774443</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9526862.570395045</v>
+        <v>9526862.570395041</v>
       </c>
     </row>
   </sheetData>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>820998.4149583185</v>
+        <v>820998.4149583187</v>
       </c>
       <c r="C2" t="n">
-        <v>820998.4149583187</v>
+        <v>820998.4149583186</v>
       </c>
       <c r="D2" t="n">
         <v>820998.4149583187</v>
@@ -26281,7 +26281,7 @@
         <v>703513.5887661945</v>
       </c>
       <c r="F2" t="n">
-        <v>703513.5887661946</v>
+        <v>703513.5887661945</v>
       </c>
       <c r="G2" t="n">
         <v>703513.5887661946</v>
@@ -26290,28 +26290,28 @@
         <v>703513.5887661945</v>
       </c>
       <c r="I2" t="n">
-        <v>703513.5887661944</v>
+        <v>703513.5887661943</v>
       </c>
       <c r="J2" t="n">
-        <v>646408.6376350459</v>
+        <v>646408.6376350458</v>
       </c>
       <c r="K2" t="n">
-        <v>678372.5625261953</v>
+        <v>678372.562526195</v>
       </c>
       <c r="L2" t="n">
-        <v>678372.5625261953</v>
+        <v>678372.5625261951</v>
       </c>
       <c r="M2" t="n">
-        <v>678372.5625261952</v>
+        <v>678372.562526195</v>
       </c>
       <c r="N2" t="n">
-        <v>678372.5625261953</v>
+        <v>678372.562526195</v>
       </c>
       <c r="O2" t="n">
-        <v>349383.8649394668</v>
+        <v>349383.8649394665</v>
       </c>
       <c r="P2" t="n">
-        <v>314689.9125394666</v>
+        <v>314689.9125394662</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>399745.2113715087</v>
+        <v>401186.0837655473</v>
       </c>
       <c r="C4" t="n">
-        <v>398484.0751896107</v>
+        <v>399924.9475836493</v>
       </c>
       <c r="D4" t="n">
-        <v>397221.2281977673</v>
+        <v>398662.1005918061</v>
       </c>
       <c r="E4" t="n">
-        <v>310120.7327196089</v>
+        <v>310858.325467664</v>
       </c>
       <c r="F4" t="n">
-        <v>309035.007903681</v>
+        <v>309772.6006517361</v>
       </c>
       <c r="G4" t="n">
-        <v>307947.7848282422</v>
+        <v>308685.3775762974</v>
       </c>
       <c r="H4" t="n">
-        <v>306859.052749216</v>
+        <v>307596.6454972712</v>
       </c>
       <c r="I4" t="n">
-        <v>305768.8007825365</v>
+        <v>306506.3935305917</v>
       </c>
       <c r="J4" t="n">
-        <v>271844.3217336416</v>
+        <v>272575.4570477202</v>
       </c>
       <c r="K4" t="n">
-        <v>289021.4139554286</v>
+        <v>289670.5133299399</v>
       </c>
       <c r="L4" t="n">
-        <v>287965.8103759362</v>
+        <v>288614.9097504474</v>
       </c>
       <c r="M4" t="n">
-        <v>286908.6980528706</v>
+        <v>287557.7974273817</v>
       </c>
       <c r="N4" t="n">
-        <v>285850.0657780665</v>
+        <v>286499.1651525777</v>
       </c>
       <c r="O4" t="n">
-        <v>97979.41103665355</v>
+        <v>99248.77312489889</v>
       </c>
       <c r="P4" t="n">
-        <v>77935.00895775885</v>
+        <v>79251.43845616035</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-139969.5964131902</v>
+        <v>-141410.4688072285</v>
       </c>
       <c r="C6" t="n">
-        <v>364560.539768708</v>
+        <v>363119.6673746693</v>
       </c>
       <c r="D6" t="n">
-        <v>365823.3867605514</v>
+        <v>364382.5143665126</v>
       </c>
       <c r="E6" t="n">
-        <v>220543.0640465856</v>
+        <v>219805.4712985305</v>
       </c>
       <c r="F6" t="n">
-        <v>356028.7888625136</v>
+        <v>355291.1961144584</v>
       </c>
       <c r="G6" t="n">
-        <v>357116.0119379524</v>
+        <v>356378.4191898972</v>
       </c>
       <c r="H6" t="n">
-        <v>358204.7440169785</v>
+        <v>357467.1512689233</v>
       </c>
       <c r="I6" t="n">
-        <v>359294.9959836579</v>
+        <v>358557.4032356026</v>
       </c>
       <c r="J6" t="n">
-        <v>145307.1729014043</v>
+        <v>144576.0375873256</v>
       </c>
       <c r="K6" t="n">
-        <v>341168.9705707667</v>
+        <v>340519.8711962551</v>
       </c>
       <c r="L6" t="n">
-        <v>354224.5741502591</v>
+        <v>353575.4747757477</v>
       </c>
       <c r="M6" t="n">
-        <v>355281.6864733246</v>
+        <v>354632.5870988132</v>
       </c>
       <c r="N6" t="n">
-        <v>356340.3187481288</v>
+        <v>355691.2193736173</v>
       </c>
       <c r="O6" t="n">
-        <v>227580.4189028132</v>
+        <v>226311.0568145676</v>
       </c>
       <c r="P6" t="n">
-        <v>214191.9035817078</v>
+        <v>212875.4740833059</v>
       </c>
     </row>
   </sheetData>
@@ -27451,10 +27451,10 @@
         <v>400.0000000000002</v>
       </c>
       <c r="H2" t="n">
-        <v>143.429703929658</v>
+        <v>390.429703929658</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>83.90259686861427</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27600,19 +27600,19 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.27387284153</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>195.3273972369997</v>
+        <v>221.9251261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>153.4774556201183</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -27630,7 +27630,7 @@
         <v>400.0000000000002</v>
       </c>
       <c r="O4" t="n">
-        <v>400.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>400.0000000000002</v>
@@ -27642,10 +27642,10 @@
         <v>400.0000000000002</v>
       </c>
       <c r="S4" t="n">
-        <v>348.9544797028555</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>206.7345665062577</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -27654,10 +27654,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>37.34953887287929</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -27673,25 +27673,25 @@
         <v>400.0000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>400.0000000000001</v>
+        <v>202.4745782429939</v>
       </c>
       <c r="D5" t="n">
         <v>400.0000000000001</v>
       </c>
       <c r="E5" t="n">
+        <v>157.3632896068686</v>
+      </c>
+      <c r="F5" t="n">
+        <v>330.3813260287687</v>
+      </c>
+      <c r="G5" t="n">
         <v>400.0000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>400.0000000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>155.0407893724433</v>
       </c>
       <c r="H5" t="n">
         <v>143.429703929658</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>83.90259686861427</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27831,7 +27831,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>101.5769052016108</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>285.5362180555555</v>
@@ -27840,13 +27840,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>237.0835276850608</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>244.27387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>221.9251261016186</v>
       </c>
       <c r="I7" t="n">
         <v>153.4774556201183</v>
@@ -27907,28 +27907,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>157.3632896068686</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>157.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>155.0407893724433</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>390.429703929658</v>
       </c>
       <c r="I8" t="n">
-        <v>83.90259686861427</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,28 +27955,28 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>143.0492973207568</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>391.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
     </row>
     <row r="9">
@@ -28043,7 +28043,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -28052,7 +28052,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -28086,13 +28086,13 @@
         <v>221.9251261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>153.4774556201183</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>199.0607738011431</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>309.0696281577792</v>
@@ -28101,19 +28101,19 @@
         <v>399.9306114025499</v>
       </c>
       <c r="N10" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="O10" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="Q10" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="R10" t="n">
-        <v>400</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="S10" t="n">
         <v>348.9544797028555</v>
@@ -28125,16 +28125,16 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>84.28208769200789</v>
+        <v>216.0623426256458</v>
       </c>
     </row>
     <row r="11">
@@ -28177,10 +28177,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="N11" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28247,7 +28247,7 @@
         <v>168</v>
       </c>
       <c r="J12" t="n">
-        <v>94.31872559980114</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>168</v>
@@ -28256,13 +28256,13 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>168</v>
+        <v>94.31872559980141</v>
       </c>
       <c r="P12" t="n">
         <v>168</v>
@@ -28414,7 +28414,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>168</v>
+        <v>14.54957336883178</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -28484,7 +28484,7 @@
         <v>168</v>
       </c>
       <c r="J15" t="n">
-        <v>38.47915862252844</v>
+        <v>168</v>
       </c>
       <c r="K15" t="n">
         <v>168</v>
@@ -28493,10 +28493,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="N15" t="n">
-        <v>168</v>
+        <v>111.9077034777898</v>
       </c>
       <c r="O15" t="n">
         <v>168</v>
@@ -28505,7 +28505,7 @@
         <v>168</v>
       </c>
       <c r="Q15" t="n">
-        <v>55.83956697727202</v>
+        <v>102.4924834390157</v>
       </c>
       <c r="R15" t="n">
         <v>168</v>
@@ -28651,10 +28651,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>168</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -28724,7 +28724,7 @@
         <v>168</v>
       </c>
       <c r="K18" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -28736,13 +28736,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
+        <v>94.3187255998011</v>
+      </c>
+      <c r="P18" t="n">
         <v>168</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
-        <v>94.31872559980103</v>
+        <v>168</v>
       </c>
       <c r="R18" t="n">
         <v>168</v>
@@ -28888,10 +28888,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>14.54957336883171</v>
       </c>
       <c r="N20" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -28961,22 +28961,22 @@
         <v>168</v>
       </c>
       <c r="K21" t="n">
+        <v>102.4924834390158</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>168</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
+        <v>111.9077034777898</v>
+      </c>
+      <c r="O21" t="n">
         <v>168</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
-        <v>94.31872559980168</v>
+        <v>168</v>
       </c>
       <c r="Q21" t="n">
         <v>168</v>
@@ -29125,10 +29125,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="N23" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -29195,25 +29195,25 @@
         <v>168</v>
       </c>
       <c r="J24" t="n">
-        <v>94.31872559980145</v>
+        <v>168</v>
       </c>
       <c r="K24" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>94.31872559980134</v>
       </c>
       <c r="M24" t="n">
         <v>168</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>168</v>
@@ -29335,7 +29335,7 @@
         <v>147</v>
       </c>
       <c r="D26" t="n">
-        <v>147</v>
+        <v>146.9999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>147</v>
@@ -29350,7 +29350,7 @@
         <v>147</v>
       </c>
       <c r="I26" t="n">
-        <v>120.0685560240971</v>
+        <v>147</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="N26" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29432,25 +29432,25 @@
         <v>147</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="K27" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>147</v>
       </c>
       <c r="O27" t="n">
-        <v>140.7014844453271</v>
+        <v>90.14150943396224</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="Q27" t="n">
         <v>147</v>
@@ -29569,7 +29569,7 @@
         <v>162</v>
       </c>
       <c r="C29" t="n">
-        <v>161.9999999999999</v>
+        <v>162</v>
       </c>
       <c r="D29" t="n">
         <v>162</v>
@@ -29599,7 +29599,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>7.728415521400093</v>
       </c>
       <c r="N29" t="n">
         <v>162</v>
@@ -29669,13 +29669,13 @@
         <v>162</v>
       </c>
       <c r="J30" t="n">
+        <v>15.48248474671647</v>
+      </c>
+      <c r="K30" t="n">
         <v>162</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
-        <v>89.20675334397482</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>162</v>
@@ -29687,16 +29687,16 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>148.1004997787264</v>
       </c>
       <c r="Q30" t="n">
-        <v>162</v>
+        <v>73.1147623208054</v>
       </c>
       <c r="R30" t="n">
         <v>162</v>
       </c>
       <c r="S30" t="n">
-        <v>162</v>
+        <v>161.9999999999999</v>
       </c>
       <c r="T30" t="n">
         <v>162</v>
@@ -29836,10 +29836,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>54.20750764360609</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>63.95180716320841</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -29906,25 +29906,25 @@
         <v>162</v>
       </c>
       <c r="J33" t="n">
-        <v>82.28534018122998</v>
+        <v>162</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>132.576876205451</v>
+        <v>132.5768762054507</v>
       </c>
       <c r="M33" t="n">
         <v>162</v>
       </c>
       <c r="N33" t="n">
-        <v>111.9077034777898</v>
+        <v>162</v>
       </c>
       <c r="O33" t="n">
-        <v>140.7014844453274</v>
+        <v>140.7014844453271</v>
       </c>
       <c r="P33" t="n">
-        <v>148.1004997787267</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>162</v>
@@ -29933,7 +29933,7 @@
         <v>162</v>
       </c>
       <c r="S33" t="n">
-        <v>162</v>
+        <v>161.9999999999999</v>
       </c>
       <c r="T33" t="n">
         <v>162</v>
@@ -30073,7 +30073,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>122.4200390775111</v>
+        <v>122.4200390775094</v>
       </c>
       <c r="N35" t="n">
         <v>162</v>
@@ -30143,25 +30143,25 @@
         <v>162</v>
       </c>
       <c r="J36" t="n">
-        <v>162</v>
+        <v>15.48248474671647</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>70.41520394891353</v>
       </c>
       <c r="M36" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>118.7812804254252</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>140.7014844453271</v>
       </c>
       <c r="P36" t="n">
-        <v>21.38045356638438</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>162</v>
@@ -30313,7 +30313,7 @@
         <v>162</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>122.4200390775092</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -30380,13 +30380,13 @@
         <v>162</v>
       </c>
       <c r="J39" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>89.20675334397539</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>21.38045356638282</v>
       </c>
       <c r="M39" t="n">
         <v>162</v>
@@ -30407,7 +30407,7 @@
         <v>162</v>
       </c>
       <c r="S39" t="n">
-        <v>162</v>
+        <v>161.9999999999999</v>
       </c>
       <c r="T39" t="n">
         <v>162</v>
@@ -31106,7 +31106,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L2" t="n">
-        <v>247.0000000000005</v>
+        <v>247.000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>301.4169396984925</v>
@@ -31343,7 +31343,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L5" t="n">
-        <v>247.0000000000005</v>
+        <v>247.0000000000006</v>
       </c>
       <c r="M5" t="n">
         <v>301.4169396984925</v>
@@ -31580,7 +31580,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L8" t="n">
-        <v>247.0000000000003</v>
+        <v>247.000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>301.4169396984925</v>
@@ -31817,7 +31817,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L11" t="n">
-        <v>247.0000000000006</v>
+        <v>247.0000000000003</v>
       </c>
       <c r="M11" t="n">
         <v>301.4169396984925</v>
@@ -32054,7 +32054,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L14" t="n">
-        <v>247.0000000000003</v>
+        <v>247.0000000000005</v>
       </c>
       <c r="M14" t="n">
         <v>301.4169396984925</v>
@@ -32291,7 +32291,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L17" t="n">
-        <v>247.0000000000008</v>
+        <v>247.0000000000007</v>
       </c>
       <c r="M17" t="n">
         <v>301.4169396984925</v>
@@ -32528,7 +32528,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L20" t="n">
-        <v>247.0000000000005</v>
+        <v>247.0000000000006</v>
       </c>
       <c r="M20" t="n">
         <v>301.4169396984925</v>
@@ -33236,10 +33236,10 @@
         <v>145.6928291457287</v>
       </c>
       <c r="K29" t="n">
-        <v>218.0000000000005</v>
+        <v>218.0000000000002</v>
       </c>
       <c r="L29" t="n">
-        <v>218.0000000000005</v>
+        <v>218.0000000000003</v>
       </c>
       <c r="M29" t="n">
         <v>301.4169396984925</v>
@@ -33248,10 +33248,10 @@
         <v>306.2941809045226</v>
       </c>
       <c r="O29" t="n">
-        <v>288.2478695740926</v>
+        <v>288.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>218.2870600406816</v>
+        <v>218.2870600406814</v>
       </c>
       <c r="Q29" t="n">
         <v>185.3716432160804</v>
@@ -33473,10 +33473,10 @@
         <v>145.6928291457287</v>
       </c>
       <c r="K32" t="n">
+        <v>218.0000000000002</v>
+      </c>
+      <c r="L32" t="n">
         <v>218.0000000000001</v>
-      </c>
-      <c r="L32" t="n">
-        <v>218.0000000000005</v>
       </c>
       <c r="M32" t="n">
         <v>301.4169396984925</v>
@@ -33485,10 +33485,10 @@
         <v>306.2941809045226</v>
       </c>
       <c r="O32" t="n">
-        <v>288.2478695740928</v>
+        <v>288.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>218.2870600406817</v>
+        <v>218.2870600406814</v>
       </c>
       <c r="Q32" t="n">
         <v>185.3716432160804</v>
@@ -33710,10 +33710,10 @@
         <v>145.6928291457287</v>
       </c>
       <c r="K35" t="n">
+        <v>218.0000000000002</v>
+      </c>
+      <c r="L35" t="n">
         <v>218.0000000000003</v>
-      </c>
-      <c r="L35" t="n">
-        <v>218.0000000000006</v>
       </c>
       <c r="M35" t="n">
         <v>301.4169396984925</v>
@@ -33722,10 +33722,10 @@
         <v>306.2941809045226</v>
       </c>
       <c r="O35" t="n">
-        <v>288.2478695740929</v>
+        <v>288.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>218.2870600406818</v>
+        <v>218.2870600406814</v>
       </c>
       <c r="Q35" t="n">
         <v>185.3716432160804</v>
@@ -33950,7 +33950,7 @@
         <v>218.0000000000002</v>
       </c>
       <c r="L38" t="n">
-        <v>218.0000000000006</v>
+        <v>218.0000000000003</v>
       </c>
       <c r="M38" t="n">
         <v>301.4169396984925</v>
@@ -33959,10 +33959,10 @@
         <v>306.2941809045226</v>
       </c>
       <c r="O38" t="n">
-        <v>288.2478695740929</v>
+        <v>288.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>218.2870600406818</v>
+        <v>218.2870600406815</v>
       </c>
       <c r="Q38" t="n">
         <v>185.3716432160804</v>
@@ -34184,7 +34184,7 @@
         <v>145.6928291457287</v>
       </c>
       <c r="K41" t="n">
-        <v>218.0000000000005</v>
+        <v>218.0000000000002</v>
       </c>
       <c r="L41" t="n">
         <v>218.0000000000003</v>
@@ -34196,10 +34196,10 @@
         <v>306.2941809045226</v>
       </c>
       <c r="O41" t="n">
-        <v>288.2478695740929</v>
+        <v>288.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>218.2870600406822</v>
+        <v>218.2870600406815</v>
       </c>
       <c r="Q41" t="n">
         <v>185.3716432160804</v>
@@ -34424,7 +34424,7 @@
         <v>218</v>
       </c>
       <c r="L44" t="n">
-        <v>218.0000000000002</v>
+        <v>218</v>
       </c>
       <c r="M44" t="n">
         <v>301.4169396984925</v>
@@ -34433,10 +34433,10 @@
         <v>306.2941809045226</v>
       </c>
       <c r="O44" t="n">
-        <v>288.2478695740929</v>
+        <v>288.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>218.2870600406818</v>
+        <v>218.2870600406814</v>
       </c>
       <c r="Q44" t="n">
         <v>185.3716432160804</v>
@@ -34749,7 +34749,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L2" t="n">
-        <v>247.0000000000004</v>
+        <v>247.0000000000011</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -34825,10 +34825,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>81.69757800437925</v>
+        <v>247</v>
       </c>
       <c r="L3" t="n">
-        <v>85.42312379454928</v>
+        <v>89.82218624425572</v>
       </c>
       <c r="M3" t="n">
         <v>247</v>
@@ -34837,7 +34837,7 @@
         <v>247</v>
       </c>
       <c r="O3" t="n">
-        <v>247</v>
+        <v>77.29851555467286</v>
       </c>
       <c r="P3" t="n">
         <v>69.89950022127358</v>
@@ -34986,7 +34986,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L5" t="n">
-        <v>247.0000000000004</v>
+        <v>247.0000000000006</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -35059,10 +35059,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>30.76495832716433</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>43.53360434381555</v>
+        <v>247</v>
       </c>
       <c r="L6" t="n">
         <v>85.42312379454928</v>
@@ -35071,7 +35071,7 @@
         <v>247</v>
       </c>
       <c r="N6" t="n">
-        <v>247</v>
+        <v>74.29856267097988</v>
       </c>
       <c r="O6" t="n">
         <v>77.29851555467286</v>
@@ -35223,7 +35223,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L8" t="n">
-        <v>247.0000000000004</v>
+        <v>247.0000000000011</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35296,7 +35296,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>207.8654581058909</v>
       </c>
       <c r="K9" t="n">
         <v>43.53360434381555</v>
@@ -35305,16 +35305,16 @@
         <v>85.42312379454928</v>
       </c>
       <c r="M9" t="n">
-        <v>108.0634738818373</v>
+        <v>247</v>
       </c>
       <c r="N9" t="n">
         <v>247</v>
       </c>
       <c r="O9" t="n">
-        <v>247</v>
+        <v>77.29851555467286</v>
       </c>
       <c r="P9" t="n">
-        <v>247</v>
+        <v>69.89950022127358</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35460,7 +35460,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L11" t="n">
-        <v>247.0000000000006</v>
+        <v>247.0000000000003</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35533,22 +35533,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>78.83624085308467</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>211.5336043438156</v>
       </c>
       <c r="L12" t="n">
-        <v>92.29190802462736</v>
+        <v>85.42312379454928</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>159.3862994833613</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>245.2985155546729</v>
+        <v>171.6172411544743</v>
       </c>
       <c r="P12" t="n">
         <v>237.8995002212736</v>
@@ -35697,7 +35697,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L14" t="n">
-        <v>247.0000000000003</v>
+        <v>247.0000000000005</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -35770,7 +35770,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>22.99667387581198</v>
+        <v>152.5175152532835</v>
       </c>
       <c r="K15" t="n">
         <v>211.5336043438156</v>
@@ -35779,19 +35779,19 @@
         <v>85.42312379454928</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>15.97022173439683</v>
       </c>
       <c r="N15" t="n">
-        <v>165.7682844513524</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>245.2985155546729</v>
       </c>
       <c r="P15" t="n">
-        <v>247</v>
+        <v>237.8995002212736</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>29.37772111821035</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35934,7 +35934,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L17" t="n">
-        <v>247.0000000000008</v>
+        <v>247.0000000000007</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -36007,28 +36007,28 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>152.5175152532835</v>
+        <v>247</v>
       </c>
       <c r="K18" t="n">
-        <v>211.5336043438156</v>
+        <v>43.53360434381555</v>
       </c>
       <c r="L18" t="n">
         <v>85.42312379454928</v>
       </c>
       <c r="M18" t="n">
-        <v>192.1439795736117</v>
+        <v>71.28579970463541</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>245.2985155546729</v>
+        <v>171.617241154474</v>
       </c>
       <c r="P18" t="n">
-        <v>69.89950022127358</v>
+        <v>247</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.20396327899563</v>
+        <v>112.160433022728</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36171,7 +36171,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L20" t="n">
-        <v>247.0000000000004</v>
+        <v>247.0000000000006</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -36247,22 +36247,22 @@
         <v>152.5175152532835</v>
       </c>
       <c r="K21" t="n">
-        <v>211.5336043438156</v>
+        <v>146.0260877828314</v>
       </c>
       <c r="L21" t="n">
         <v>85.42312379454928</v>
       </c>
       <c r="M21" t="n">
-        <v>136.0516830514009</v>
+        <v>15.97022173439683</v>
       </c>
       <c r="N21" t="n">
-        <v>56.09229652221023</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>77.29851555467286</v>
+        <v>245.2985155546729</v>
       </c>
       <c r="P21" t="n">
-        <v>164.2182258210753</v>
+        <v>237.8995002212736</v>
       </c>
       <c r="Q21" t="n">
         <v>94.8852376791946</v>
@@ -36408,7 +36408,7 @@
         <v>218.355783919598</v>
       </c>
       <c r="L23" t="n">
-        <v>247.0000000000005</v>
+        <v>247.0000000000004</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36481,28 +36481,28 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>152.5175152532835</v>
+      </c>
+      <c r="K24" t="n">
+        <v>43.53360434381555</v>
+      </c>
+      <c r="L24" t="n">
         <v>247</v>
       </c>
-      <c r="K24" t="n">
-        <v>211.5336043438156</v>
-      </c>
-      <c r="L24" t="n">
-        <v>85.42312379454928</v>
-      </c>
       <c r="M24" t="n">
-        <v>23.98022042669615</v>
+        <v>15.97022173439683</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>89.93892744470456</v>
       </c>
       <c r="O24" t="n">
-        <v>77.29851555467286</v>
+        <v>247</v>
       </c>
       <c r="P24" t="n">
-        <v>237.8995002212736</v>
+        <v>69.89950022127358</v>
       </c>
       <c r="Q24" t="n">
-        <v>94.8852376791946</v>
+        <v>112.160433022728</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,7 +36642,7 @@
         <v>110.6498229006383</v>
       </c>
       <c r="K26" t="n">
-        <v>218.0000000000004</v>
+        <v>218.0000000000003</v>
       </c>
       <c r="L26" t="n">
         <v>218.0000000000005</v>
@@ -36718,16 +36718,16 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>131.5175152532835</v>
       </c>
       <c r="K27" t="n">
-        <v>190.5336043438156</v>
+        <v>43.53360434381555</v>
       </c>
       <c r="L27" t="n">
-        <v>218</v>
+        <v>144.2637651721421</v>
       </c>
       <c r="M27" t="n">
-        <v>40.50608508189334</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>35.09229652221023</v>
@@ -36736,10 +36736,10 @@
         <v>218</v>
       </c>
       <c r="P27" t="n">
-        <v>69.89950022127358</v>
+        <v>216.8995002212736</v>
       </c>
       <c r="Q27" t="n">
-        <v>91.16043302272797</v>
+        <v>73.8852376791946</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36879,10 +36879,10 @@
         <v>110.6498229006383</v>
       </c>
       <c r="K29" t="n">
-        <v>218.0000000000005</v>
+        <v>218.0000000000002</v>
       </c>
       <c r="L29" t="n">
-        <v>218.0000000000005</v>
+        <v>218.0000000000003</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -36891,10 +36891,10 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>218.0000000000002</v>
+        <v>218</v>
       </c>
       <c r="P29" t="n">
-        <v>218.0000000000002</v>
+        <v>218</v>
       </c>
       <c r="Q29" t="n">
         <v>12.548958888595</v>
@@ -36955,28 +36955,28 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>146.5175152532835</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>43.53360434381555</v>
+        <v>205.5336043438156</v>
       </c>
       <c r="L30" t="n">
-        <v>174.6298771385241</v>
+        <v>218</v>
       </c>
       <c r="M30" t="n">
-        <v>212.3353724789464</v>
+        <v>9.97022173439683</v>
       </c>
       <c r="N30" t="n">
         <v>50.09229652221023</v>
       </c>
       <c r="O30" t="n">
-        <v>77.29851555467286</v>
+        <v>161.5957965914967</v>
       </c>
       <c r="P30" t="n">
-        <v>69.89950022127358</v>
+        <v>218</v>
       </c>
       <c r="Q30" t="n">
-        <v>88.8852376791946</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,11 +37116,11 @@
         <v>110.6498229006383</v>
       </c>
       <c r="K32" t="n">
+        <v>218.0000000000002</v>
+      </c>
+      <c r="L32" t="n">
         <v>218.0000000000001</v>
       </c>
-      <c r="L32" t="n">
-        <v>218.0000000000005</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -37128,10 +37128,10 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="P32" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="Q32" t="n">
         <v>12.548958888595</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>66.80285543451352</v>
+        <v>164.8110586910284</v>
       </c>
       <c r="K33" t="n">
         <v>43.53360434381555</v>
       </c>
       <c r="L33" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="M33" t="n">
         <v>9.97022173439683</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>50.09229652221023</v>
       </c>
       <c r="O33" t="n">
-        <v>218.0000000000003</v>
+        <v>218</v>
       </c>
       <c r="P33" t="n">
-        <v>218.0000000000003</v>
+        <v>69.89950022127358</v>
       </c>
       <c r="Q33" t="n">
         <v>88.8852376791946</v>
@@ -37353,10 +37353,10 @@
         <v>110.6498229006383</v>
       </c>
       <c r="K35" t="n">
-        <v>218.0000000000004</v>
+        <v>218.0000000000002</v>
       </c>
       <c r="L35" t="n">
-        <v>218.0000000000006</v>
+        <v>218.0000000000003</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -37365,10 +37365,10 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="P35" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="Q35" t="n">
         <v>12.548958888595</v>
@@ -37429,25 +37429,25 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>146.5175152532835</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>43.53360434381555</v>
       </c>
       <c r="L36" t="n">
-        <v>85.42312379454928</v>
+        <v>218</v>
       </c>
       <c r="M36" t="n">
-        <v>9.97022173439683</v>
+        <v>218</v>
       </c>
       <c r="N36" t="n">
-        <v>218.0000000000004</v>
+        <v>6.873576947635463</v>
       </c>
       <c r="O36" t="n">
-        <v>179.5822625990237</v>
+        <v>218</v>
       </c>
       <c r="P36" t="n">
-        <v>91.27995378765797</v>
+        <v>69.89950022127358</v>
       </c>
       <c r="Q36" t="n">
         <v>88.8852376791946</v>
@@ -37593,7 +37593,7 @@
         <v>218.0000000000003</v>
       </c>
       <c r="L38" t="n">
-        <v>218.0000000000006</v>
+        <v>218.0000000000003</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -37602,10 +37602,10 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="P38" t="n">
-        <v>218.0000000000004</v>
+        <v>218.0000000000001</v>
       </c>
       <c r="Q38" t="n">
         <v>12.548958888595</v>
@@ -37666,16 +37666,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>146.5175152532835</v>
+        <v>211.982257181072</v>
       </c>
       <c r="K39" t="n">
-        <v>132.7403576877909</v>
+        <v>43.53360434381555</v>
       </c>
       <c r="L39" t="n">
-        <v>85.42312379454928</v>
+        <v>146.1545908330238</v>
       </c>
       <c r="M39" t="n">
-        <v>64.23487270022001</v>
+        <v>9.97022173439683</v>
       </c>
       <c r="N39" t="n">
         <v>50.09229652221023</v>
@@ -37684,10 +37684,10 @@
         <v>77.29851555467286</v>
       </c>
       <c r="P39" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="Q39" t="n">
-        <v>88.8852376791946</v>
+        <v>106.160433022728</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37827,7 +37827,7 @@
         <v>110.6498229006383</v>
       </c>
       <c r="K41" t="n">
-        <v>218.0000000000004</v>
+        <v>218.0000000000002</v>
       </c>
       <c r="L41" t="n">
         <v>218.0000000000003</v>
@@ -37839,10 +37839,10 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="P41" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="Q41" t="n">
         <v>12.548958888595</v>
@@ -37906,22 +37906,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>43.53360434381555</v>
+        <v>209.1919191919193</v>
       </c>
       <c r="L42" t="n">
-        <v>100.4231237945493</v>
+        <v>218</v>
       </c>
       <c r="M42" t="n">
-        <v>190.9366754988834</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>92.29851555467286</v>
+        <v>218</v>
       </c>
       <c r="P42" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38067,7 +38067,7 @@
         <v>218</v>
       </c>
       <c r="L44" t="n">
-        <v>218.0000000000002</v>
+        <v>218</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -38076,10 +38076,10 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="P44" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="Q44" t="n">
         <v>12.548958888595</v>
@@ -38143,19 +38143,19 @@
         <v>211.982257181072</v>
       </c>
       <c r="K45" t="n">
-        <v>43.53360434381555</v>
+        <v>145.3101617895736</v>
       </c>
       <c r="L45" t="n">
-        <v>218.0000000000004</v>
+        <v>218</v>
       </c>
       <c r="M45" t="n">
-        <v>218.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>101.7765574457602</v>
+        <v>218</v>
       </c>
       <c r="P45" t="n">
         <v>69.89950022127358</v>
